--- a/jefferson_city.xlsx
+++ b/jefferson_city.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17950" uniqueCount="2008">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17959" uniqueCount="2008">
   <si>
     <t>Scheme Listing by CRID for ZIP Codes 65101 / 65109</t>
   </si>
@@ -6034,7 +6034,7 @@
     <t>ZION HILL</t>
   </si>
   <si>
-    <t>Total Line items: 1993</t>
+    <t>Total Line items: 1994</t>
   </si>
 </sst>
 </file>
@@ -6423,7 +6423,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1996"/>
+  <dimension ref="A1:I1997"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="8" customWidth="1"/>
@@ -46610,7 +46610,7 @@
         <v>61</v>
       </c>
       <c r="B1387" s="3" t="s">
-        <v>249</v>
+        <v>583</v>
       </c>
       <c r="C1387" s="1" t="s">
         <v>8</v>
@@ -56670,10 +56670,10 @@
     </row>
     <row r="1734" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1734" s="3" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B1734" s="3" t="s">
-        <v>707</v>
+        <v>224</v>
       </c>
       <c r="C1734" s="1" t="s">
         <v>8</v>
@@ -56685,7 +56685,7 @@
         <v>1779</v>
       </c>
       <c r="F1734" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1734" t="s">
         <v>9</v>
@@ -56699,7 +56699,7 @@
     </row>
     <row r="1735" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1735" s="3" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B1735" s="3" t="s">
         <v>707</v>
@@ -56711,10 +56711,10 @@
         <v>9</v>
       </c>
       <c r="E1735" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="F1735" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G1735" t="s">
         <v>9</v>
@@ -56728,10 +56728,10 @@
     </row>
     <row r="1736" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1736" s="3" t="s">
-        <v>135</v>
+        <v>308</v>
       </c>
       <c r="B1736" s="3" t="s">
-        <v>419</v>
+        <v>707</v>
       </c>
       <c r="C1736" s="1" t="s">
         <v>8</v>
@@ -56743,7 +56743,7 @@
         <v>1780</v>
       </c>
       <c r="F1736" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1736" t="s">
         <v>9</v>
@@ -56757,10 +56757,10 @@
     </row>
     <row r="1737" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1737" s="3" t="s">
-        <v>61</v>
+        <v>135</v>
       </c>
       <c r="B1737" s="3" t="s">
-        <v>253</v>
+        <v>419</v>
       </c>
       <c r="C1737" s="1" t="s">
         <v>8</v>
@@ -56769,7 +56769,7 @@
         <v>9</v>
       </c>
       <c r="E1737" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="F1737" t="s">
         <v>29</v>
@@ -56781,15 +56781,15 @@
         <v>18</v>
       </c>
       <c r="I1737" s="1" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1738" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1738" s="3" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="B1738" s="3" t="s">
-        <v>789</v>
+        <v>253</v>
       </c>
       <c r="C1738" s="1" t="s">
         <v>8</v>
@@ -56801,7 +56801,7 @@
         <v>1781</v>
       </c>
       <c r="F1738" t="s">
-        <v>321</v>
+        <v>29</v>
       </c>
       <c r="G1738" t="s">
         <v>9</v>
@@ -56815,10 +56815,10 @@
     </row>
     <row r="1739" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1739" s="3" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="B1739" s="3" t="s">
-        <v>103</v>
+        <v>789</v>
       </c>
       <c r="C1739" s="1" t="s">
         <v>8</v>
@@ -56827,10 +56827,10 @@
         <v>9</v>
       </c>
       <c r="E1739" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="F1739" t="s">
-        <v>11</v>
+        <v>321</v>
       </c>
       <c r="G1739" t="s">
         <v>9</v>
@@ -56839,15 +56839,15 @@
         <v>18</v>
       </c>
       <c r="I1739" s="1" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1740" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1740" s="3" t="s">
-        <v>1350</v>
+        <v>102</v>
       </c>
       <c r="B1740" s="3" t="s">
-        <v>1783</v>
+        <v>103</v>
       </c>
       <c r="C1740" s="1" t="s">
         <v>8</v>
@@ -56856,27 +56856,27 @@
         <v>9</v>
       </c>
       <c r="E1740" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="F1740" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="G1740" t="s">
         <v>9</v>
       </c>
       <c r="H1740" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1740" s="1" t="s">
-        <v>13</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1741" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1741" s="3" t="s">
-        <v>83</v>
+        <v>1350</v>
       </c>
       <c r="B1741" s="3" t="s">
-        <v>84</v>
+        <v>1783</v>
       </c>
       <c r="C1741" s="1" t="s">
         <v>8</v>
@@ -56885,27 +56885,27 @@
         <v>9</v>
       </c>
       <c r="E1741" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="F1741" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="G1741" t="s">
         <v>9</v>
       </c>
       <c r="H1741" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1741" s="1" t="s">
-        <v>130</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1742" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1742" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B1742" s="3" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="C1742" s="1" t="s">
         <v>8</v>
@@ -56914,10 +56914,10 @@
         <v>9</v>
       </c>
       <c r="E1742" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="F1742" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="G1742" t="s">
         <v>9</v>
@@ -56926,7 +56926,7 @@
         <v>18</v>
       </c>
       <c r="I1742" s="1" t="s">
-        <v>340</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1743" spans="1:9" x14ac:dyDescent="0.25">
@@ -56934,7 +56934,7 @@
         <v>91</v>
       </c>
       <c r="B1743" s="3" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="C1743" s="1" t="s">
         <v>8</v>
@@ -56943,10 +56943,10 @@
         <v>9</v>
       </c>
       <c r="E1743" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="F1743" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1743" t="s">
         <v>9</v>
@@ -56960,10 +56960,10 @@
     </row>
     <row r="1744" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1744" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B1744" s="3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C1744" s="1" t="s">
         <v>8</v>
@@ -56972,10 +56972,10 @@
         <v>9</v>
       </c>
       <c r="E1744" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="F1744" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G1744" t="s">
         <v>9</v>
@@ -56984,7 +56984,7 @@
         <v>18</v>
       </c>
       <c r="I1744" s="1" t="s">
-        <v>78</v>
+        <v>340</v>
       </c>
     </row>
     <row r="1745" spans="1:9" x14ac:dyDescent="0.25">
@@ -57004,7 +57004,7 @@
         <v>1788</v>
       </c>
       <c r="F1745" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1745" t="s">
         <v>9</v>
@@ -57018,10 +57018,10 @@
     </row>
     <row r="1746" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1746" s="3" t="s">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B1746" s="3" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="C1746" s="1" t="s">
         <v>8</v>
@@ -57030,7 +57030,7 @@
         <v>9</v>
       </c>
       <c r="E1746" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="F1746" t="s">
         <v>29</v>
@@ -57039,18 +57039,18 @@
         <v>9</v>
       </c>
       <c r="H1746" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1746" s="1" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1747" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1747" s="3" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="B1747" s="3" t="s">
-        <v>253</v>
+        <v>27</v>
       </c>
       <c r="C1747" s="1" t="s">
         <v>8</v>
@@ -57059,27 +57059,27 @@
         <v>9</v>
       </c>
       <c r="E1747" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="F1747" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="G1747" t="s">
         <v>9</v>
       </c>
       <c r="H1747" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1747" s="1" t="s">
-        <v>281</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1748" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1748" s="3" t="s">
-        <v>1093</v>
+        <v>70</v>
       </c>
       <c r="B1748" s="3" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="C1748" s="1" t="s">
         <v>8</v>
@@ -57088,27 +57088,27 @@
         <v>9</v>
       </c>
       <c r="E1748" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="F1748" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="G1748" t="s">
         <v>9</v>
       </c>
       <c r="H1748" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1748" s="1" t="s">
-        <v>160</v>
+        <v>281</v>
       </c>
     </row>
     <row r="1749" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1749" s="3" t="s">
-        <v>275</v>
+        <v>1093</v>
       </c>
       <c r="B1749" s="3" t="s">
-        <v>179</v>
+        <v>283</v>
       </c>
       <c r="C1749" s="1" t="s">
         <v>8</v>
@@ -57120,24 +57120,24 @@
         <v>1791</v>
       </c>
       <c r="F1749" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G1749" t="s">
         <v>9</v>
       </c>
       <c r="H1749" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1749" s="1" t="s">
-        <v>340</v>
+        <v>160</v>
       </c>
     </row>
     <row r="1750" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1750" s="3" t="s">
-        <v>399</v>
+        <v>275</v>
       </c>
       <c r="B1750" s="3" t="s">
-        <v>15</v>
+        <v>179</v>
       </c>
       <c r="C1750" s="1" t="s">
         <v>8</v>
@@ -57146,27 +57146,27 @@
         <v>9</v>
       </c>
       <c r="E1750" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="F1750" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1750" t="s">
         <v>9</v>
       </c>
       <c r="H1750" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1750" s="1" t="s">
-        <v>95</v>
+        <v>340</v>
       </c>
     </row>
     <row r="1751" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1751" s="3" t="s">
-        <v>26</v>
+        <v>399</v>
       </c>
       <c r="B1751" s="3" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C1751" s="1" t="s">
         <v>8</v>
@@ -57175,27 +57175,27 @@
         <v>9</v>
       </c>
       <c r="E1751" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="F1751" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G1751" t="s">
         <v>9</v>
       </c>
       <c r="H1751" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1751" s="1" t="s">
-        <v>340</v>
+        <v>95</v>
       </c>
     </row>
     <row r="1752" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1752" s="3" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B1752" s="3" t="s">
-        <v>484</v>
+        <v>27</v>
       </c>
       <c r="C1752" s="1" t="s">
         <v>8</v>
@@ -57204,10 +57204,10 @@
         <v>9</v>
       </c>
       <c r="E1752" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="F1752" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="G1752" t="s">
         <v>9</v>
@@ -57221,10 +57221,10 @@
     </row>
     <row r="1753" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1753" s="3" t="s">
-        <v>462</v>
+        <v>39</v>
       </c>
       <c r="B1753" s="3" t="s">
-        <v>58</v>
+        <v>484</v>
       </c>
       <c r="C1753" s="1" t="s">
         <v>8</v>
@@ -57233,24 +57233,24 @@
         <v>9</v>
       </c>
       <c r="E1753" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="F1753" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="G1753" t="s">
         <v>9</v>
       </c>
       <c r="H1753" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1753" s="1" t="s">
-        <v>13</v>
+        <v>340</v>
       </c>
     </row>
     <row r="1754" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1754" s="3" t="s">
-        <v>190</v>
+        <v>462</v>
       </c>
       <c r="B1754" s="3" t="s">
         <v>58</v>
@@ -57262,10 +57262,10 @@
         <v>9</v>
       </c>
       <c r="E1754" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="F1754" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G1754" t="s">
         <v>9</v>
@@ -57274,15 +57274,15 @@
         <v>12</v>
       </c>
       <c r="I1754" s="1" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1755" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1755" s="3" t="s">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="B1755" s="3" t="s">
-        <v>1037</v>
+        <v>58</v>
       </c>
       <c r="C1755" s="1" t="s">
         <v>8</v>
@@ -57291,7 +57291,7 @@
         <v>9</v>
       </c>
       <c r="E1755" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="F1755" t="s">
         <v>45</v>
@@ -57300,18 +57300,18 @@
         <v>9</v>
       </c>
       <c r="H1755" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1755" s="1" t="s">
-        <v>323</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1756" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1756" s="3" t="s">
-        <v>415</v>
+        <v>75</v>
       </c>
       <c r="B1756" s="3" t="s">
-        <v>400</v>
+        <v>1037</v>
       </c>
       <c r="C1756" s="1" t="s">
         <v>8</v>
@@ -57320,10 +57320,10 @@
         <v>9</v>
       </c>
       <c r="E1756" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="F1756" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1756" t="s">
         <v>9</v>
@@ -57332,15 +57332,15 @@
         <v>18</v>
       </c>
       <c r="I1756" s="1" t="s">
-        <v>46</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1757" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1757" s="3" t="s">
-        <v>301</v>
+        <v>415</v>
       </c>
       <c r="B1757" s="3" t="s">
-        <v>212</v>
+        <v>400</v>
       </c>
       <c r="C1757" s="1" t="s">
         <v>8</v>
@@ -57349,10 +57349,10 @@
         <v>9</v>
       </c>
       <c r="E1757" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="F1757" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G1757" t="s">
         <v>9</v>
@@ -57361,15 +57361,15 @@
         <v>18</v>
       </c>
       <c r="I1757" s="1" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1758" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1758" s="3" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="B1758" s="3" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="C1758" s="1" t="s">
         <v>8</v>
@@ -57378,10 +57378,10 @@
         <v>9</v>
       </c>
       <c r="E1758" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="F1758" t="s">
-        <v>955</v>
+        <v>42</v>
       </c>
       <c r="G1758" t="s">
         <v>9</v>
@@ -57390,15 +57390,15 @@
         <v>18</v>
       </c>
       <c r="I1758" s="1" t="s">
-        <v>252</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1759" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1759" s="3" t="s">
-        <v>39</v>
+        <v>277</v>
       </c>
       <c r="B1759" s="3" t="s">
-        <v>103</v>
+        <v>253</v>
       </c>
       <c r="C1759" s="1" t="s">
         <v>8</v>
@@ -57419,15 +57419,15 @@
         <v>18</v>
       </c>
       <c r="I1759" s="1" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
     </row>
     <row r="1760" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1760" s="3" t="s">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="B1760" s="3" t="s">
-        <v>158</v>
+        <v>103</v>
       </c>
       <c r="C1760" s="1" t="s">
         <v>8</v>
@@ -57436,10 +57436,10 @@
         <v>9</v>
       </c>
       <c r="E1760" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="F1760" t="s">
-        <v>45</v>
+        <v>955</v>
       </c>
       <c r="G1760" t="s">
         <v>9</v>
@@ -57448,15 +57448,15 @@
         <v>18</v>
       </c>
       <c r="I1760" s="1" t="s">
-        <v>78</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1761" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1761" s="3" t="s">
-        <v>195</v>
+        <v>131</v>
       </c>
       <c r="B1761" s="3" t="s">
-        <v>280</v>
+        <v>158</v>
       </c>
       <c r="C1761" s="1" t="s">
         <v>8</v>
@@ -57468,24 +57468,24 @@
         <v>1801</v>
       </c>
       <c r="F1761" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="G1761" t="s">
         <v>9</v>
       </c>
       <c r="H1761" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1761" s="1" t="s">
-        <v>187</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1762" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1762" s="3" t="s">
-        <v>277</v>
+        <v>195</v>
       </c>
       <c r="B1762" s="3" t="s">
-        <v>32</v>
+        <v>280</v>
       </c>
       <c r="C1762" s="1" t="s">
         <v>8</v>
@@ -57494,27 +57494,27 @@
         <v>9</v>
       </c>
       <c r="E1762" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="F1762" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G1762" t="s">
         <v>9</v>
       </c>
       <c r="H1762" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1762" s="1" t="s">
-        <v>46</v>
+        <v>187</v>
       </c>
     </row>
     <row r="1763" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1763" s="3" t="s">
-        <v>206</v>
+        <v>277</v>
       </c>
       <c r="B1763" s="3" t="s">
-        <v>207</v>
+        <v>32</v>
       </c>
       <c r="C1763" s="1" t="s">
         <v>8</v>
@@ -57523,10 +57523,10 @@
         <v>9</v>
       </c>
       <c r="E1763" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="F1763" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G1763" t="s">
         <v>9</v>
@@ -57535,15 +57535,15 @@
         <v>18</v>
       </c>
       <c r="I1763" s="1" t="s">
-        <v>141</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1764" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1764" s="3" t="s">
-        <v>102</v>
+        <v>206</v>
       </c>
       <c r="B1764" s="3" t="s">
-        <v>103</v>
+        <v>207</v>
       </c>
       <c r="C1764" s="1" t="s">
         <v>8</v>
@@ -57555,7 +57555,7 @@
         <v>1803</v>
       </c>
       <c r="F1764" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="G1764" t="s">
         <v>9</v>
@@ -57569,10 +57569,10 @@
     </row>
     <row r="1765" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1765" s="3" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="B1765" s="3" t="s">
-        <v>475</v>
+        <v>103</v>
       </c>
       <c r="C1765" s="1" t="s">
         <v>8</v>
@@ -57581,27 +57581,27 @@
         <v>9</v>
       </c>
       <c r="E1765" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="F1765" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="G1765" t="s">
         <v>9</v>
       </c>
       <c r="H1765" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1765" s="1" t="s">
-        <v>225</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1766" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1766" s="3" t="s">
-        <v>469</v>
+        <v>14</v>
       </c>
       <c r="B1766" s="3" t="s">
-        <v>535</v>
+        <v>475</v>
       </c>
       <c r="C1766" s="1" t="s">
         <v>8</v>
@@ -57610,7 +57610,7 @@
         <v>9</v>
       </c>
       <c r="E1766" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="F1766" t="s">
         <v>45</v>
@@ -57619,18 +57619,18 @@
         <v>9</v>
       </c>
       <c r="H1766" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1766" s="1" t="s">
-        <v>444</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1767" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1767" s="3" t="s">
-        <v>228</v>
+        <v>469</v>
       </c>
       <c r="B1767" s="3" t="s">
-        <v>381</v>
+        <v>535</v>
       </c>
       <c r="C1767" s="1" t="s">
         <v>8</v>
@@ -57639,10 +57639,10 @@
         <v>9</v>
       </c>
       <c r="E1767" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="F1767" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1767" t="s">
         <v>9</v>
@@ -57651,15 +57651,15 @@
         <v>18</v>
       </c>
       <c r="I1767" s="1" t="s">
-        <v>314</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1768" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1768" s="3" t="s">
-        <v>610</v>
+        <v>228</v>
       </c>
       <c r="B1768" s="3" t="s">
-        <v>241</v>
+        <v>381</v>
       </c>
       <c r="C1768" s="1" t="s">
         <v>8</v>
@@ -57668,10 +57668,10 @@
         <v>9</v>
       </c>
       <c r="E1768" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="F1768" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G1768" t="s">
         <v>9</v>
@@ -57680,36 +57680,36 @@
         <v>18</v>
       </c>
       <c r="I1768" s="1" t="s">
-        <v>133</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1769" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1769" s="3" t="s">
-        <v>57</v>
+        <v>610</v>
       </c>
       <c r="B1769" s="3" t="s">
-        <v>137</v>
+        <v>241</v>
       </c>
       <c r="C1769" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1769" t="s">
-        <v>186</v>
+        <v>9</v>
       </c>
       <c r="E1769" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="F1769" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="G1769" t="s">
         <v>9</v>
       </c>
       <c r="H1769" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1769" s="1" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
     </row>
     <row r="1770" spans="1:9" x14ac:dyDescent="0.25">
@@ -57723,13 +57723,13 @@
         <v>8</v>
       </c>
       <c r="D1770" t="s">
-        <v>9</v>
+        <v>186</v>
       </c>
       <c r="E1770" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="F1770" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="G1770" t="s">
         <v>9</v>
@@ -57738,15 +57738,15 @@
         <v>12</v>
       </c>
       <c r="I1770" s="1" t="s">
-        <v>30</v>
+        <v>187</v>
       </c>
     </row>
     <row r="1771" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1771" s="3" t="s">
-        <v>585</v>
+        <v>57</v>
       </c>
       <c r="B1771" s="3" t="s">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="C1771" s="1" t="s">
         <v>8</v>
@@ -57758,7 +57758,7 @@
         <v>1809</v>
       </c>
       <c r="F1771" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="G1771" t="s">
         <v>9</v>
@@ -57767,15 +57767,15 @@
         <v>12</v>
       </c>
       <c r="I1771" s="1" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1772" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1772" s="3" t="s">
-        <v>39</v>
+        <v>585</v>
       </c>
       <c r="B1772" s="3" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="C1772" s="1" t="s">
         <v>8</v>
@@ -57787,7 +57787,7 @@
         <v>1809</v>
       </c>
       <c r="F1772" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G1772" t="s">
         <v>9</v>
@@ -57796,15 +57796,15 @@
         <v>12</v>
       </c>
       <c r="I1772" s="1" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
     </row>
     <row r="1773" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1773" s="3" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="B1773" s="3" t="s">
-        <v>1037</v>
+        <v>27</v>
       </c>
       <c r="C1773" s="1" t="s">
         <v>8</v>
@@ -57825,15 +57825,15 @@
         <v>12</v>
       </c>
       <c r="I1773" s="1" t="s">
-        <v>239</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1774" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1774" s="3" t="s">
-        <v>585</v>
+        <v>91</v>
       </c>
       <c r="B1774" s="3" t="s">
-        <v>1810</v>
+        <v>1037</v>
       </c>
       <c r="C1774" s="1" t="s">
         <v>8</v>
@@ -57854,15 +57854,15 @@
         <v>12</v>
       </c>
       <c r="I1774" s="1" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
     </row>
     <row r="1775" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1775" s="3" t="s">
-        <v>1811</v>
+        <v>585</v>
       </c>
       <c r="B1775" s="3" t="s">
-        <v>292</v>
+        <v>1810</v>
       </c>
       <c r="C1775" s="1" t="s">
         <v>8</v>
@@ -57883,15 +57883,15 @@
         <v>12</v>
       </c>
       <c r="I1775" s="1" t="s">
-        <v>220</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1776" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1776" s="3" t="s">
-        <v>474</v>
+        <v>1811</v>
       </c>
       <c r="B1776" s="3" t="s">
-        <v>25</v>
+        <v>292</v>
       </c>
       <c r="C1776" s="1" t="s">
         <v>8</v>
@@ -57903,7 +57903,7 @@
         <v>1809</v>
       </c>
       <c r="F1776" t="s">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="G1776" t="s">
         <v>9</v>
@@ -57912,15 +57912,15 @@
         <v>12</v>
       </c>
       <c r="I1776" s="1" t="s">
-        <v>51</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1777" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1777" s="3" t="s">
-        <v>379</v>
+        <v>474</v>
       </c>
       <c r="B1777" s="3" t="s">
-        <v>735</v>
+        <v>25</v>
       </c>
       <c r="C1777" s="1" t="s">
         <v>8</v>
@@ -57929,10 +57929,10 @@
         <v>9</v>
       </c>
       <c r="E1777" t="s">
-        <v>1812</v>
+        <v>1809</v>
       </c>
       <c r="F1777" t="s">
-        <v>45</v>
+        <v>295</v>
       </c>
       <c r="G1777" t="s">
         <v>9</v>
@@ -57946,10 +57946,10 @@
     </row>
     <row r="1778" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1778" s="3" t="s">
-        <v>36</v>
+        <v>379</v>
       </c>
       <c r="B1778" s="3" t="s">
-        <v>196</v>
+        <v>735</v>
       </c>
       <c r="C1778" s="1" t="s">
         <v>8</v>
@@ -57958,19 +57958,19 @@
         <v>9</v>
       </c>
       <c r="E1778" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="F1778" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1778" t="s">
         <v>9</v>
       </c>
       <c r="H1778" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1778" s="1" t="s">
-        <v>209</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1779" spans="1:9" x14ac:dyDescent="0.25">
@@ -57978,7 +57978,7 @@
         <v>36</v>
       </c>
       <c r="B1779" s="3" t="s">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="C1779" s="1" t="s">
         <v>8</v>
@@ -57987,27 +57987,27 @@
         <v>9</v>
       </c>
       <c r="E1779" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="F1779" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="G1779" t="s">
         <v>9</v>
       </c>
       <c r="H1779" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1779" s="1" t="s">
-        <v>51</v>
+        <v>209</v>
       </c>
     </row>
     <row r="1780" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1780" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B1780" s="3" t="s">
-        <v>450</v>
+        <v>253</v>
       </c>
       <c r="C1780" s="1" t="s">
         <v>8</v>
@@ -58016,10 +58016,10 @@
         <v>9</v>
       </c>
       <c r="E1780" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="F1780" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="G1780" t="s">
         <v>9</v>
@@ -58028,27 +58028,27 @@
         <v>12</v>
       </c>
       <c r="I1780" s="1" t="s">
-        <v>185</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1781" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1781" s="3" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="B1781" s="3" t="s">
-        <v>88</v>
+        <v>450</v>
       </c>
       <c r="C1781" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1781" t="s">
-        <v>260</v>
+        <v>9</v>
       </c>
       <c r="E1781" t="s">
         <v>1815</v>
       </c>
       <c r="F1781" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G1781" t="s">
         <v>9</v>
@@ -58057,7 +58057,7 @@
         <v>12</v>
       </c>
       <c r="I1781" s="1" t="s">
-        <v>385</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1782" spans="1:9" x14ac:dyDescent="0.25">
@@ -58065,13 +58065,13 @@
         <v>61</v>
       </c>
       <c r="B1782" s="3" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="C1782" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1782" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E1782" t="s">
         <v>1815</v>
@@ -58091,22 +58091,22 @@
     </row>
     <row r="1783" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1783" s="3" t="s">
-        <v>1126</v>
+        <v>61</v>
       </c>
       <c r="B1783" s="3" t="s">
-        <v>400</v>
+        <v>62</v>
       </c>
       <c r="C1783" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1783" t="s">
-        <v>9</v>
+        <v>263</v>
       </c>
       <c r="E1783" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="F1783" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="G1783" t="s">
         <v>9</v>
@@ -58115,15 +58115,15 @@
         <v>12</v>
       </c>
       <c r="I1783" s="1" t="s">
-        <v>13</v>
+        <v>385</v>
       </c>
     </row>
     <row r="1784" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1784" s="3" t="s">
-        <v>386</v>
+        <v>1126</v>
       </c>
       <c r="B1784" s="3" t="s">
-        <v>521</v>
+        <v>400</v>
       </c>
       <c r="C1784" s="1" t="s">
         <v>8</v>
@@ -58132,27 +58132,27 @@
         <v>9</v>
       </c>
       <c r="E1784" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="F1784" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="G1784" t="s">
         <v>9</v>
       </c>
       <c r="H1784" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1784" s="1" t="s">
-        <v>130</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1785" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1785" s="3" t="s">
-        <v>195</v>
+        <v>386</v>
       </c>
       <c r="B1785" s="3" t="s">
-        <v>196</v>
+        <v>521</v>
       </c>
       <c r="C1785" s="1" t="s">
         <v>8</v>
@@ -58161,62 +58161,62 @@
         <v>9</v>
       </c>
       <c r="E1785" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="F1785" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="G1785" t="s">
         <v>9</v>
       </c>
       <c r="H1785" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1785" s="1" t="s">
-        <v>23</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1786" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1786" s="3" t="s">
-        <v>638</v>
+        <v>195</v>
       </c>
       <c r="B1786" s="3" t="s">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="C1786" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1786" t="s">
-        <v>260</v>
+        <v>9</v>
       </c>
       <c r="E1786" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="F1786" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G1786" t="s">
         <v>9</v>
       </c>
       <c r="H1786" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1786" s="1" t="s">
-        <v>120</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1787" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1787" s="3" t="s">
-        <v>327</v>
+        <v>638</v>
       </c>
       <c r="B1787" s="3" t="s">
-        <v>99</v>
+        <v>163</v>
       </c>
       <c r="C1787" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1787" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E1787" t="s">
         <v>1819</v>
@@ -58231,15 +58231,15 @@
         <v>18</v>
       </c>
       <c r="I1787" s="1" t="s">
-        <v>314</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1788" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1788" s="3" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B1788" s="3" t="s">
-        <v>271</v>
+        <v>99</v>
       </c>
       <c r="C1788" s="1" t="s">
         <v>8</v>
@@ -58260,15 +58260,15 @@
         <v>18</v>
       </c>
       <c r="I1788" s="1" t="s">
-        <v>120</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1789" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1789" s="3" t="s">
-        <v>638</v>
+        <v>319</v>
       </c>
       <c r="B1789" s="3" t="s">
-        <v>535</v>
+        <v>271</v>
       </c>
       <c r="C1789" s="1" t="s">
         <v>8</v>
@@ -58289,27 +58289,27 @@
         <v>18</v>
       </c>
       <c r="I1789" s="1" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1790" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1790" s="3" t="s">
-        <v>61</v>
+        <v>638</v>
       </c>
       <c r="B1790" s="3" t="s">
-        <v>62</v>
+        <v>535</v>
       </c>
       <c r="C1790" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1790" t="s">
-        <v>9</v>
+        <v>263</v>
       </c>
       <c r="E1790" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="F1790" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G1790" t="s">
         <v>9</v>
@@ -58318,15 +58318,15 @@
         <v>18</v>
       </c>
       <c r="I1790" s="1" t="s">
-        <v>169</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1791" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1791" s="3" t="s">
-        <v>200</v>
+        <v>61</v>
       </c>
       <c r="B1791" s="3" t="s">
-        <v>222</v>
+        <v>62</v>
       </c>
       <c r="C1791" s="1" t="s">
         <v>8</v>
@@ -58338,7 +58338,7 @@
         <v>1820</v>
       </c>
       <c r="F1791" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1791" t="s">
         <v>9</v>
@@ -58352,10 +58352,10 @@
     </row>
     <row r="1792" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1792" s="3" t="s">
-        <v>474</v>
+        <v>200</v>
       </c>
       <c r="B1792" s="3" t="s">
-        <v>25</v>
+        <v>222</v>
       </c>
       <c r="C1792" s="1" t="s">
         <v>8</v>
@@ -58364,27 +58364,27 @@
         <v>9</v>
       </c>
       <c r="E1792" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="F1792" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G1792" t="s">
         <v>9</v>
       </c>
       <c r="H1792" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1792" s="1" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="1793" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1793" s="3" t="s">
-        <v>65</v>
+        <v>474</v>
       </c>
       <c r="B1793" s="3" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="C1793" s="1" t="s">
         <v>8</v>
@@ -58393,27 +58393,27 @@
         <v>9</v>
       </c>
       <c r="E1793" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="F1793" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G1793" t="s">
         <v>9</v>
       </c>
       <c r="H1793" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1793" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="1794" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1794" s="3" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="B1794" s="3" t="s">
-        <v>253</v>
+        <v>88</v>
       </c>
       <c r="C1794" s="1" t="s">
         <v>8</v>
@@ -58422,27 +58422,27 @@
         <v>9</v>
       </c>
       <c r="E1794" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="F1794" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="G1794" t="s">
         <v>9</v>
       </c>
       <c r="H1794" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1794" s="1" t="s">
-        <v>23</v>
+        <v>167</v>
       </c>
     </row>
     <row r="1795" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1795" s="3" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="B1795" s="3" t="s">
-        <v>108</v>
+        <v>253</v>
       </c>
       <c r="C1795" s="1" t="s">
         <v>8</v>
@@ -58451,10 +58451,10 @@
         <v>9</v>
       </c>
       <c r="E1795" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="F1795" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="G1795" t="s">
         <v>9</v>
@@ -58463,15 +58463,15 @@
         <v>12</v>
       </c>
       <c r="I1795" s="1" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1796" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1796" s="3" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="B1796" s="3" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="C1796" s="1" t="s">
         <v>8</v>
@@ -58480,27 +58480,27 @@
         <v>9</v>
       </c>
       <c r="E1796" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="F1796" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G1796" t="s">
         <v>9</v>
       </c>
       <c r="H1796" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1796" s="1" t="s">
-        <v>60</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1797" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1797" s="3" t="s">
-        <v>275</v>
+        <v>57</v>
       </c>
       <c r="B1797" s="3" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="C1797" s="1" t="s">
         <v>8</v>
@@ -58509,10 +58509,10 @@
         <v>9</v>
       </c>
       <c r="E1797" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="F1797" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G1797" t="s">
         <v>9</v>
@@ -58521,15 +58521,15 @@
         <v>18</v>
       </c>
       <c r="I1797" s="1" t="s">
-        <v>340</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1798" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1798" s="3" t="s">
-        <v>68</v>
+        <v>275</v>
       </c>
       <c r="B1798" s="3" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="C1798" s="1" t="s">
         <v>8</v>
@@ -58538,10 +58538,10 @@
         <v>9</v>
       </c>
       <c r="E1798" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="F1798" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G1798" t="s">
         <v>9</v>
@@ -58550,15 +58550,15 @@
         <v>18</v>
       </c>
       <c r="I1798" s="1" t="s">
-        <v>46</v>
+        <v>340</v>
       </c>
     </row>
     <row r="1799" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1799" s="3" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="B1799" s="3" t="s">
-        <v>53</v>
+        <v>243</v>
       </c>
       <c r="C1799" s="1" t="s">
         <v>8</v>
@@ -58567,10 +58567,10 @@
         <v>9</v>
       </c>
       <c r="E1799" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="F1799" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G1799" t="s">
         <v>9</v>
@@ -58579,15 +58579,15 @@
         <v>18</v>
       </c>
       <c r="I1799" s="1" t="s">
-        <v>281</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1800" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1800" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B1800" s="3" t="s">
-        <v>349</v>
+        <v>53</v>
       </c>
       <c r="C1800" s="1" t="s">
         <v>8</v>
@@ -58599,7 +58599,7 @@
         <v>1828</v>
       </c>
       <c r="F1800" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1800" t="s">
         <v>9</v>
@@ -58613,10 +58613,10 @@
     </row>
     <row r="1801" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1801" s="3" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="B1801" s="3" t="s">
-        <v>419</v>
+        <v>349</v>
       </c>
       <c r="C1801" s="1" t="s">
         <v>8</v>
@@ -58625,19 +58625,19 @@
         <v>9</v>
       </c>
       <c r="E1801" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="F1801" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G1801" t="s">
         <v>9</v>
       </c>
       <c r="H1801" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1801" s="1" t="s">
-        <v>143</v>
+        <v>281</v>
       </c>
     </row>
     <row r="1802" spans="1:9" x14ac:dyDescent="0.25">
@@ -58654,27 +58654,27 @@
         <v>9</v>
       </c>
       <c r="E1802" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="F1802" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G1802" t="s">
         <v>9</v>
       </c>
       <c r="H1802" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1802" s="1" t="s">
-        <v>340</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1803" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1803" s="3" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="B1803" s="3" t="s">
-        <v>115</v>
+        <v>419</v>
       </c>
       <c r="C1803" s="1" t="s">
         <v>8</v>
@@ -58686,24 +58686,24 @@
         <v>1830</v>
       </c>
       <c r="F1803" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="G1803" t="s">
         <v>9</v>
       </c>
       <c r="H1803" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1803" s="1" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
     </row>
     <row r="1804" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1804" s="3" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B1804" s="3" t="s">
-        <v>419</v>
+        <v>115</v>
       </c>
       <c r="C1804" s="1" t="s">
         <v>8</v>
@@ -58715,24 +58715,24 @@
         <v>1830</v>
       </c>
       <c r="F1804" t="s">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="G1804" t="s">
         <v>9</v>
       </c>
       <c r="H1804" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1804" s="1" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1805" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1805" s="3" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="B1805" s="3" t="s">
-        <v>193</v>
+        <v>419</v>
       </c>
       <c r="C1805" s="1" t="s">
         <v>8</v>
@@ -58741,10 +58741,10 @@
         <v>9</v>
       </c>
       <c r="E1805" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="F1805" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="G1805" t="s">
         <v>9</v>
@@ -58753,15 +58753,15 @@
         <v>18</v>
       </c>
       <c r="I1805" s="1" t="s">
-        <v>46</v>
+        <v>340</v>
       </c>
     </row>
     <row r="1806" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1806" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="B1806" s="3" t="s">
-        <v>137</v>
+        <v>193</v>
       </c>
       <c r="C1806" s="1" t="s">
         <v>8</v>
@@ -58770,10 +58770,10 @@
         <v>9</v>
       </c>
       <c r="E1806" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="F1806" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1806" t="s">
         <v>9</v>
@@ -58782,15 +58782,15 @@
         <v>18</v>
       </c>
       <c r="I1806" s="1" t="s">
-        <v>151</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1807" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1807" s="3" t="s">
-        <v>627</v>
+        <v>57</v>
       </c>
       <c r="B1807" s="3" t="s">
-        <v>513</v>
+        <v>137</v>
       </c>
       <c r="C1807" s="1" t="s">
         <v>8</v>
@@ -58799,10 +58799,10 @@
         <v>9</v>
       </c>
       <c r="E1807" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="F1807" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G1807" t="s">
         <v>9</v>
@@ -58811,15 +58811,15 @@
         <v>18</v>
       </c>
       <c r="I1807" s="1" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
     </row>
     <row r="1808" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1808" s="3" t="s">
-        <v>250</v>
+        <v>627</v>
       </c>
       <c r="B1808" s="3" t="s">
-        <v>193</v>
+        <v>513</v>
       </c>
       <c r="C1808" s="1" t="s">
         <v>8</v>
@@ -58828,27 +58828,27 @@
         <v>9</v>
       </c>
       <c r="E1808" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="F1808" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G1808" t="s">
         <v>9</v>
       </c>
       <c r="H1808" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1808" s="1" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1809" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1809" s="3" t="s">
-        <v>91</v>
+        <v>250</v>
       </c>
       <c r="B1809" s="3" t="s">
-        <v>92</v>
+        <v>193</v>
       </c>
       <c r="C1809" s="1" t="s">
         <v>8</v>
@@ -58857,7 +58857,7 @@
         <v>9</v>
       </c>
       <c r="E1809" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="F1809" t="s">
         <v>42</v>
@@ -58866,18 +58866,18 @@
         <v>9</v>
       </c>
       <c r="H1809" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1809" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1810" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1810" s="3" t="s">
-        <v>399</v>
+        <v>91</v>
       </c>
       <c r="B1810" s="3" t="s">
-        <v>475</v>
+        <v>92</v>
       </c>
       <c r="C1810" s="1" t="s">
         <v>8</v>
@@ -58886,27 +58886,27 @@
         <v>9</v>
       </c>
       <c r="E1810" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="F1810" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G1810" t="s">
         <v>9</v>
       </c>
       <c r="H1810" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1810" s="1" t="s">
-        <v>225</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1811" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1811" s="3" t="s">
-        <v>61</v>
+        <v>399</v>
       </c>
       <c r="B1811" s="3" t="s">
-        <v>137</v>
+        <v>475</v>
       </c>
       <c r="C1811" s="1" t="s">
         <v>8</v>
@@ -58915,10 +58915,10 @@
         <v>9</v>
       </c>
       <c r="E1811" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="F1811" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="G1811" t="s">
         <v>9</v>
@@ -58927,15 +58927,15 @@
         <v>12</v>
       </c>
       <c r="I1811" s="1" t="s">
-        <v>101</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1812" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1812" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B1812" s="3" t="s">
-        <v>243</v>
+        <v>137</v>
       </c>
       <c r="C1812" s="1" t="s">
         <v>8</v>
@@ -58944,7 +58944,7 @@
         <v>9</v>
       </c>
       <c r="E1812" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="F1812" t="s">
         <v>82</v>
@@ -58953,18 +58953,18 @@
         <v>9</v>
       </c>
       <c r="H1812" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1812" s="1" t="s">
-        <v>314</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1813" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1813" s="3" t="s">
-        <v>144</v>
+        <v>68</v>
       </c>
       <c r="B1813" s="3" t="s">
-        <v>125</v>
+        <v>243</v>
       </c>
       <c r="C1813" s="1" t="s">
         <v>8</v>
@@ -58973,10 +58973,10 @@
         <v>9</v>
       </c>
       <c r="E1813" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="F1813" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="G1813" t="s">
         <v>9</v>
@@ -58985,15 +58985,15 @@
         <v>18</v>
       </c>
       <c r="I1813" s="1" t="s">
-        <v>147</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1814" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1814" s="3" t="s">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="B1814" s="3" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="C1814" s="1" t="s">
         <v>8</v>
@@ -59002,10 +59002,10 @@
         <v>9</v>
       </c>
       <c r="E1814" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="F1814" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G1814" t="s">
         <v>9</v>
@@ -59014,15 +59014,15 @@
         <v>18</v>
       </c>
       <c r="I1814" s="1" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1815" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1815" s="3" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="B1815" s="3" t="s">
-        <v>1841</v>
+        <v>84</v>
       </c>
       <c r="C1815" s="1" t="s">
         <v>8</v>
@@ -59031,10 +59031,10 @@
         <v>9</v>
       </c>
       <c r="E1815" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="F1815" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1815" t="s">
         <v>9</v>
@@ -59043,15 +59043,15 @@
         <v>18</v>
       </c>
       <c r="I1815" s="1" t="s">
-        <v>392</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1816" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1816" s="3" t="s">
-        <v>206</v>
+        <v>91</v>
       </c>
       <c r="B1816" s="3" t="s">
-        <v>156</v>
+        <v>1841</v>
       </c>
       <c r="C1816" s="1" t="s">
         <v>8</v>
@@ -59072,15 +59072,15 @@
         <v>18</v>
       </c>
       <c r="I1816" s="1" t="s">
-        <v>209</v>
+        <v>392</v>
       </c>
     </row>
     <row r="1817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1817" s="3" t="s">
-        <v>61</v>
+        <v>206</v>
       </c>
       <c r="B1817" s="3" t="s">
-        <v>62</v>
+        <v>156</v>
       </c>
       <c r="C1817" s="1" t="s">
         <v>8</v>
@@ -59089,7 +59089,7 @@
         <v>9</v>
       </c>
       <c r="E1817" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="F1817" t="s">
         <v>29</v>
@@ -59101,15 +59101,15 @@
         <v>18</v>
       </c>
       <c r="I1817" s="1" t="s">
-        <v>46</v>
+        <v>209</v>
       </c>
     </row>
     <row r="1818" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1818" s="3" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="B1818" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C1818" s="1" t="s">
         <v>8</v>
@@ -59118,10 +59118,10 @@
         <v>9</v>
       </c>
       <c r="E1818" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="F1818" t="s">
-        <v>734</v>
+        <v>29</v>
       </c>
       <c r="G1818" t="s">
         <v>9</v>
@@ -59130,15 +59130,15 @@
         <v>18</v>
       </c>
       <c r="I1818" s="1" t="s">
-        <v>281</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1819" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1819" s="3" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="B1819" s="3" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="C1819" s="1" t="s">
         <v>8</v>
@@ -59147,39 +59147,39 @@
         <v>9</v>
       </c>
       <c r="E1819" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="F1819" t="s">
-        <v>42</v>
+        <v>734</v>
       </c>
       <c r="G1819" t="s">
         <v>9</v>
       </c>
       <c r="H1819" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1819" s="1" t="s">
-        <v>13</v>
+        <v>281</v>
       </c>
     </row>
     <row r="1820" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1820" s="3" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B1820" s="3" t="s">
-        <v>37</v>
+        <v>137</v>
       </c>
       <c r="C1820" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1820" t="s">
-        <v>263</v>
+        <v>9</v>
       </c>
       <c r="E1820" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="F1820" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1820" t="s">
         <v>9</v>
@@ -59188,44 +59188,44 @@
         <v>12</v>
       </c>
       <c r="I1820" s="1" t="s">
-        <v>220</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1821" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1821" s="3" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="B1821" s="3" t="s">
-        <v>762</v>
+        <v>37</v>
       </c>
       <c r="C1821" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1821" t="s">
-        <v>9</v>
+        <v>263</v>
       </c>
       <c r="E1821" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F1821" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G1821" t="s">
         <v>9</v>
       </c>
       <c r="H1821" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1821" s="1" t="s">
-        <v>314</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1822" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1822" s="3" t="s">
-        <v>206</v>
+        <v>135</v>
       </c>
       <c r="B1822" s="3" t="s">
-        <v>207</v>
+        <v>762</v>
       </c>
       <c r="C1822" s="1" t="s">
         <v>8</v>
@@ -59234,10 +59234,10 @@
         <v>9</v>
       </c>
       <c r="E1822" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F1822" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G1822" t="s">
         <v>9</v>
@@ -59246,15 +59246,15 @@
         <v>18</v>
       </c>
       <c r="I1822" s="1" t="s">
-        <v>340</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1823" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1823" s="3" t="s">
-        <v>68</v>
+        <v>206</v>
       </c>
       <c r="B1823" s="3" t="s">
-        <v>37</v>
+        <v>207</v>
       </c>
       <c r="C1823" s="1" t="s">
         <v>8</v>
@@ -59263,10 +59263,10 @@
         <v>9</v>
       </c>
       <c r="E1823" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F1823" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1823" t="s">
         <v>9</v>
@@ -59275,15 +59275,15 @@
         <v>18</v>
       </c>
       <c r="I1823" s="1" t="s">
-        <v>444</v>
+        <v>340</v>
       </c>
     </row>
     <row r="1824" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1824" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B1824" s="3" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="C1824" s="1" t="s">
         <v>8</v>
@@ -59295,7 +59295,7 @@
         <v>1849</v>
       </c>
       <c r="F1824" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G1824" t="s">
         <v>9</v>
@@ -59304,15 +59304,15 @@
         <v>18</v>
       </c>
       <c r="I1824" s="1" t="s">
-        <v>60</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1825" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1825" s="3" t="s">
-        <v>275</v>
+        <v>57</v>
       </c>
       <c r="B1825" s="3" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="C1825" s="1" t="s">
         <v>8</v>
@@ -59321,10 +59321,10 @@
         <v>9</v>
       </c>
       <c r="E1825" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="F1825" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G1825" t="s">
         <v>9</v>
@@ -59333,27 +59333,27 @@
         <v>18</v>
       </c>
       <c r="I1825" s="1" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1826" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1826" s="3" t="s">
-        <v>802</v>
+        <v>275</v>
       </c>
       <c r="B1826" s="3" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C1826" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1826" t="s">
-        <v>186</v>
+        <v>9</v>
       </c>
       <c r="E1826" t="s">
         <v>1850</v>
       </c>
       <c r="F1826" t="s">
-        <v>376</v>
+        <v>29</v>
       </c>
       <c r="G1826" t="s">
         <v>9</v>
@@ -59362,15 +59362,15 @@
         <v>18</v>
       </c>
       <c r="I1826" s="1" t="s">
-        <v>444</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1827" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1827" s="3" t="s">
-        <v>124</v>
+        <v>802</v>
       </c>
       <c r="B1827" s="3" t="s">
-        <v>521</v>
+        <v>158</v>
       </c>
       <c r="C1827" s="1" t="s">
         <v>8</v>
@@ -59391,27 +59391,27 @@
         <v>18</v>
       </c>
       <c r="I1827" s="1" t="s">
-        <v>90</v>
+        <v>444</v>
       </c>
     </row>
     <row r="1828" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1828" s="3" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="B1828" s="3" t="s">
-        <v>99</v>
+        <v>521</v>
       </c>
       <c r="C1828" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1828" t="s">
-        <v>9</v>
+        <v>186</v>
       </c>
       <c r="E1828" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="F1828" t="s">
-        <v>42</v>
+        <v>376</v>
       </c>
       <c r="G1828" t="s">
         <v>9</v>
@@ -59420,15 +59420,15 @@
         <v>18</v>
       </c>
       <c r="I1828" s="1" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1829" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1829" s="3" t="s">
-        <v>517</v>
+        <v>96</v>
       </c>
       <c r="B1829" s="3" t="s">
-        <v>207</v>
+        <v>99</v>
       </c>
       <c r="C1829" s="1" t="s">
         <v>8</v>
@@ -59437,10 +59437,10 @@
         <v>9</v>
       </c>
       <c r="E1829" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="F1829" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G1829" t="s">
         <v>9</v>
@@ -59449,15 +59449,15 @@
         <v>18</v>
       </c>
       <c r="I1829" s="1" t="s">
-        <v>19</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1830" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1830" s="3" t="s">
-        <v>627</v>
+        <v>517</v>
       </c>
       <c r="B1830" s="3" t="s">
-        <v>513</v>
+        <v>207</v>
       </c>
       <c r="C1830" s="1" t="s">
         <v>8</v>
@@ -59466,10 +59466,10 @@
         <v>9</v>
       </c>
       <c r="E1830" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="F1830" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="G1830" t="s">
         <v>9</v>
@@ -59478,15 +59478,15 @@
         <v>18</v>
       </c>
       <c r="I1830" s="1" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1831" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1831" s="3" t="s">
-        <v>1854</v>
+        <v>627</v>
       </c>
       <c r="B1831" s="3" t="s">
-        <v>1854</v>
+        <v>513</v>
       </c>
       <c r="C1831" s="1" t="s">
         <v>8</v>
@@ -59495,10 +59495,10 @@
         <v>9</v>
       </c>
       <c r="E1831" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="F1831" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G1831" t="s">
         <v>9</v>
@@ -59507,15 +59507,15 @@
         <v>18</v>
       </c>
       <c r="I1831" s="1" t="s">
-        <v>281</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1832" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1832" s="3" t="s">
-        <v>190</v>
+        <v>1854</v>
       </c>
       <c r="B1832" s="3" t="s">
-        <v>278</v>
+        <v>1854</v>
       </c>
       <c r="C1832" s="1" t="s">
         <v>8</v>
@@ -59527,7 +59527,7 @@
         <v>1855</v>
       </c>
       <c r="F1832" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1832" t="s">
         <v>9</v>
@@ -59541,10 +59541,10 @@
     </row>
     <row r="1833" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1833" s="3" t="s">
-        <v>1527</v>
+        <v>190</v>
       </c>
       <c r="B1833" s="3" t="s">
-        <v>367</v>
+        <v>278</v>
       </c>
       <c r="C1833" s="1" t="s">
         <v>8</v>
@@ -59553,7 +59553,7 @@
         <v>9</v>
       </c>
       <c r="E1833" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="F1833" t="s">
         <v>29</v>
@@ -59562,18 +59562,18 @@
         <v>9</v>
       </c>
       <c r="H1833" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1833" s="1" t="s">
-        <v>160</v>
+        <v>281</v>
       </c>
     </row>
     <row r="1834" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1834" s="3" t="s">
-        <v>610</v>
+        <v>1527</v>
       </c>
       <c r="B1834" s="3" t="s">
-        <v>1120</v>
+        <v>367</v>
       </c>
       <c r="C1834" s="1" t="s">
         <v>8</v>
@@ -59582,27 +59582,27 @@
         <v>9</v>
       </c>
       <c r="E1834" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="F1834" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="G1834" t="s">
         <v>9</v>
       </c>
       <c r="H1834" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1834" s="1" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
     </row>
     <row r="1835" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1835" s="3" t="s">
-        <v>585</v>
+        <v>610</v>
       </c>
       <c r="B1835" s="3" t="s">
-        <v>362</v>
+        <v>1120</v>
       </c>
       <c r="C1835" s="1" t="s">
         <v>8</v>
@@ -59611,7 +59611,7 @@
         <v>9</v>
       </c>
       <c r="E1835" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="F1835" t="s">
         <v>82</v>
@@ -59623,15 +59623,15 @@
         <v>18</v>
       </c>
       <c r="I1835" s="1" t="s">
-        <v>86</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1836" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1836" s="3" t="s">
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="B1836" s="3" t="s">
-        <v>954</v>
+        <v>362</v>
       </c>
       <c r="C1836" s="1" t="s">
         <v>8</v>
@@ -59640,27 +59640,27 @@
         <v>9</v>
       </c>
       <c r="E1836" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="F1836" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="G1836" t="s">
         <v>9</v>
       </c>
       <c r="H1836" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1836" s="1" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1837" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1837" s="3" t="s">
-        <v>435</v>
+        <v>565</v>
       </c>
       <c r="B1837" s="3" t="s">
-        <v>137</v>
+        <v>954</v>
       </c>
       <c r="C1837" s="1" t="s">
         <v>8</v>
@@ -59669,10 +59669,10 @@
         <v>9</v>
       </c>
       <c r="E1837" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="F1837" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G1837" t="s">
         <v>9</v>
@@ -59681,15 +59681,15 @@
         <v>12</v>
       </c>
       <c r="I1837" s="1" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1838" s="3" t="s">
-        <v>627</v>
+        <v>435</v>
       </c>
       <c r="B1838" s="3" t="s">
-        <v>513</v>
+        <v>137</v>
       </c>
       <c r="C1838" s="1" t="s">
         <v>8</v>
@@ -59698,10 +59698,10 @@
         <v>9</v>
       </c>
       <c r="E1838" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="F1838" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="G1838" t="s">
         <v>9</v>
@@ -59710,15 +59710,15 @@
         <v>12</v>
       </c>
       <c r="I1838" s="1" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1839" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1839" s="3" t="s">
-        <v>144</v>
+        <v>627</v>
       </c>
       <c r="B1839" s="3" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="C1839" s="1" t="s">
         <v>8</v>
@@ -59727,27 +59727,27 @@
         <v>9</v>
       </c>
       <c r="E1839" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="F1839" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="G1839" t="s">
         <v>9</v>
       </c>
       <c r="H1839" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1839" s="1" t="s">
-        <v>130</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1840" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1840" s="3" t="s">
-        <v>1182</v>
+        <v>144</v>
       </c>
       <c r="B1840" s="3" t="s">
-        <v>362</v>
+        <v>528</v>
       </c>
       <c r="C1840" s="1" t="s">
         <v>8</v>
@@ -59756,10 +59756,10 @@
         <v>9</v>
       </c>
       <c r="E1840" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="F1840" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G1840" t="s">
         <v>9</v>
@@ -59768,15 +59768,15 @@
         <v>18</v>
       </c>
       <c r="I1840" s="1" t="s">
-        <v>19</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1841" s="3" t="s">
-        <v>1028</v>
+        <v>1182</v>
       </c>
       <c r="B1841" s="3" t="s">
-        <v>162</v>
+        <v>362</v>
       </c>
       <c r="C1841" s="1" t="s">
         <v>8</v>
@@ -59785,27 +59785,27 @@
         <v>9</v>
       </c>
       <c r="E1841" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="F1841" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1841" t="s">
         <v>9</v>
       </c>
       <c r="H1841" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1841" s="1" t="s">
-        <v>160</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1842" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1842" s="3" t="s">
-        <v>57</v>
+        <v>1028</v>
       </c>
       <c r="B1842" s="3" t="s">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="C1842" s="1" t="s">
         <v>8</v>
@@ -59814,10 +59814,10 @@
         <v>9</v>
       </c>
       <c r="E1842" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="F1842" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G1842" t="s">
         <v>9</v>
@@ -59826,15 +59826,15 @@
         <v>12</v>
       </c>
       <c r="I1842" s="1" t="s">
-        <v>69</v>
+        <v>160</v>
       </c>
     </row>
     <row r="1843" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1843" s="3" t="s">
-        <v>313</v>
+        <v>57</v>
       </c>
       <c r="B1843" s="3" t="s">
-        <v>243</v>
+        <v>58</v>
       </c>
       <c r="C1843" s="1" t="s">
         <v>8</v>
@@ -59855,15 +59855,15 @@
         <v>12</v>
       </c>
       <c r="I1843" s="1" t="s">
-        <v>185</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1844" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1844" s="3" t="s">
-        <v>1866</v>
+        <v>313</v>
       </c>
       <c r="B1844" s="3" t="s">
-        <v>1348</v>
+        <v>243</v>
       </c>
       <c r="C1844" s="1" t="s">
         <v>8</v>
@@ -59872,27 +59872,27 @@
         <v>9</v>
       </c>
       <c r="E1844" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="F1844" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G1844" t="s">
-        <v>186</v>
+        <v>9</v>
       </c>
       <c r="H1844" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1844" s="1" t="s">
-        <v>46</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1845" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1845" s="3" t="s">
-        <v>313</v>
+        <v>1866</v>
       </c>
       <c r="B1845" s="3" t="s">
-        <v>222</v>
+        <v>1348</v>
       </c>
       <c r="C1845" s="1" t="s">
         <v>8</v>
@@ -59901,7 +59901,7 @@
         <v>9</v>
       </c>
       <c r="E1845" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="F1845" t="s">
         <v>9</v>
@@ -59913,18 +59913,18 @@
         <v>18</v>
       </c>
       <c r="I1845" s="1" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1846" s="3" t="s">
-        <v>148</v>
+        <v>313</v>
       </c>
       <c r="B1846" s="3" t="s">
-        <v>72</v>
+        <v>222</v>
       </c>
       <c r="C1846" s="1" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="D1846" t="s">
         <v>9</v>
@@ -59942,18 +59942,18 @@
         <v>18</v>
       </c>
       <c r="I1846" s="1" t="s">
-        <v>78</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1847" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1847" s="3" t="s">
-        <v>408</v>
+        <v>148</v>
       </c>
       <c r="B1847" s="3" t="s">
-        <v>409</v>
+        <v>72</v>
       </c>
       <c r="C1847" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D1847" t="s">
         <v>9</v>
@@ -59971,18 +59971,18 @@
         <v>18</v>
       </c>
       <c r="I1847" s="1" t="s">
-        <v>147</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1848" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1848" s="3" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B1848" s="3" t="s">
-        <v>722</v>
+        <v>409</v>
       </c>
       <c r="C1848" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="D1848" t="s">
         <v>9</v>
@@ -60000,15 +60000,15 @@
         <v>18</v>
       </c>
       <c r="I1848" s="1" t="s">
-        <v>78</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1849" s="3" t="s">
-        <v>1869</v>
+        <v>411</v>
       </c>
       <c r="B1849" s="3" t="s">
-        <v>1870</v>
+        <v>722</v>
       </c>
       <c r="C1849" s="1" t="s">
         <v>8</v>
@@ -60017,27 +60017,27 @@
         <v>9</v>
       </c>
       <c r="E1849" t="s">
-        <v>1871</v>
+        <v>1868</v>
       </c>
       <c r="F1849" t="s">
         <v>9</v>
       </c>
       <c r="G1849" t="s">
-        <v>9</v>
+        <v>186</v>
       </c>
       <c r="H1849" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1849" s="1" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1850" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1850" s="3" t="s">
-        <v>65</v>
+        <v>1869</v>
       </c>
       <c r="B1850" s="3" t="s">
-        <v>88</v>
+        <v>1870</v>
       </c>
       <c r="C1850" s="1" t="s">
         <v>8</v>
@@ -60046,10 +60046,10 @@
         <v>9</v>
       </c>
       <c r="E1850" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="F1850" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="G1850" t="s">
         <v>9</v>
@@ -60058,15 +60058,15 @@
         <v>12</v>
       </c>
       <c r="I1850" s="1" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1851" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1851" s="3" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="B1851" s="3" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C1851" s="1" t="s">
         <v>8</v>
@@ -60075,24 +60075,24 @@
         <v>9</v>
       </c>
       <c r="E1851" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="F1851" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="G1851" t="s">
         <v>9</v>
       </c>
       <c r="H1851" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1851" s="1" t="s">
-        <v>323</v>
+        <v>95</v>
       </c>
     </row>
     <row r="1852" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1852" s="3" t="s">
-        <v>26</v>
+        <v>102</v>
       </c>
       <c r="B1852" s="3" t="s">
         <v>103</v>
@@ -60104,7 +60104,7 @@
         <v>9</v>
       </c>
       <c r="E1852" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="F1852" t="s">
         <v>82</v>
@@ -60116,15 +60116,15 @@
         <v>18</v>
       </c>
       <c r="I1852" s="1" t="s">
-        <v>74</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1853" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1853" s="3" t="s">
-        <v>190</v>
+        <v>26</v>
       </c>
       <c r="B1853" s="3" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="C1853" s="1" t="s">
         <v>8</v>
@@ -60133,10 +60133,10 @@
         <v>9</v>
       </c>
       <c r="E1853" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="F1853" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="G1853" t="s">
         <v>9</v>
@@ -60145,7 +60145,7 @@
         <v>18</v>
       </c>
       <c r="I1853" s="1" t="s">
-        <v>246</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1854" spans="1:9" x14ac:dyDescent="0.25">
@@ -60153,7 +60153,7 @@
         <v>190</v>
       </c>
       <c r="B1854" s="3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C1854" s="1" t="s">
         <v>8</v>
@@ -60162,10 +60162,10 @@
         <v>9</v>
       </c>
       <c r="E1854" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="F1854" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G1854" t="s">
         <v>9</v>
@@ -60179,10 +60179,10 @@
     </row>
     <row r="1855" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1855" s="3" t="s">
-        <v>61</v>
+        <v>190</v>
       </c>
       <c r="B1855" s="3" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="C1855" s="1" t="s">
         <v>8</v>
@@ -60194,7 +60194,7 @@
         <v>1876</v>
       </c>
       <c r="F1855" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1855" t="s">
         <v>9</v>
@@ -60203,15 +60203,15 @@
         <v>18</v>
       </c>
       <c r="I1855" s="1" t="s">
-        <v>60</v>
+        <v>246</v>
       </c>
     </row>
     <row r="1856" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1856" s="3" t="s">
-        <v>327</v>
+        <v>61</v>
       </c>
       <c r="B1856" s="3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C1856" s="1" t="s">
         <v>8</v>
@@ -60223,7 +60223,7 @@
         <v>1876</v>
       </c>
       <c r="F1856" t="s">
-        <v>641</v>
+        <v>29</v>
       </c>
       <c r="G1856" t="s">
         <v>9</v>
@@ -60232,15 +60232,15 @@
         <v>18</v>
       </c>
       <c r="I1856" s="1" t="s">
-        <v>246</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1857" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1857" s="3" t="s">
-        <v>91</v>
+        <v>327</v>
       </c>
       <c r="B1857" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C1857" s="1" t="s">
         <v>8</v>
@@ -60249,27 +60249,27 @@
         <v>9</v>
       </c>
       <c r="E1857" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="F1857" t="s">
-        <v>45</v>
+        <v>641</v>
       </c>
       <c r="G1857" t="s">
         <v>9</v>
       </c>
       <c r="H1857" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1857" s="1" t="s">
-        <v>23</v>
+        <v>246</v>
       </c>
     </row>
     <row r="1858" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1858" s="3" t="s">
-        <v>571</v>
+        <v>91</v>
       </c>
       <c r="B1858" s="3" t="s">
-        <v>572</v>
+        <v>103</v>
       </c>
       <c r="C1858" s="1" t="s">
         <v>8</v>
@@ -60278,27 +60278,27 @@
         <v>9</v>
       </c>
       <c r="E1858" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="F1858" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1858" t="s">
         <v>9</v>
       </c>
       <c r="H1858" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1858" s="1" t="s">
-        <v>167</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1859" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1859" s="3" t="s">
-        <v>61</v>
+        <v>571</v>
       </c>
       <c r="B1859" s="3" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="C1859" s="1" t="s">
         <v>8</v>
@@ -60307,10 +60307,10 @@
         <v>9</v>
       </c>
       <c r="E1859" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="F1859" t="s">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="G1859" t="s">
         <v>9</v>
@@ -60319,21 +60319,21 @@
         <v>18</v>
       </c>
       <c r="I1859" s="1" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
     </row>
     <row r="1860" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1860" s="3" t="s">
-        <v>1880</v>
+        <v>61</v>
       </c>
       <c r="B1860" s="3" t="s">
-        <v>88</v>
+        <v>583</v>
       </c>
       <c r="C1860" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1860" t="s">
-        <v>260</v>
+        <v>9</v>
       </c>
       <c r="E1860" t="s">
         <v>1879</v>
@@ -60353,22 +60353,22 @@
     </row>
     <row r="1861" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1861" s="3" t="s">
-        <v>61</v>
+        <v>1880</v>
       </c>
       <c r="B1861" s="3" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="C1861" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1861" t="s">
-        <v>9</v>
+        <v>260</v>
       </c>
       <c r="E1861" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="F1861" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="G1861" t="s">
         <v>9</v>
@@ -60377,12 +60377,12 @@
         <v>18</v>
       </c>
       <c r="I1861" s="1" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1862" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1862" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B1862" s="3" t="s">
         <v>137</v>
@@ -60394,7 +60394,7 @@
         <v>9</v>
       </c>
       <c r="E1862" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="F1862" t="s">
         <v>45</v>
@@ -60403,18 +60403,18 @@
         <v>9</v>
       </c>
       <c r="H1862" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1862" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1863" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1863" s="3" t="s">
-        <v>190</v>
+        <v>57</v>
       </c>
       <c r="B1863" s="3" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="C1863" s="1" t="s">
         <v>8</v>
@@ -60423,7 +60423,7 @@
         <v>9</v>
       </c>
       <c r="E1863" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="F1863" t="s">
         <v>45</v>
@@ -60435,15 +60435,15 @@
         <v>12</v>
       </c>
       <c r="I1863" s="1" t="s">
-        <v>385</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1864" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1864" s="3" t="s">
-        <v>446</v>
+        <v>190</v>
       </c>
       <c r="B1864" s="3" t="s">
-        <v>265</v>
+        <v>58</v>
       </c>
       <c r="C1864" s="1" t="s">
         <v>8</v>
@@ -60452,27 +60452,27 @@
         <v>9</v>
       </c>
       <c r="E1864" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="F1864" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1864" t="s">
         <v>9</v>
       </c>
       <c r="H1864" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1864" s="1" t="s">
-        <v>203</v>
+        <v>385</v>
       </c>
     </row>
     <row r="1865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1865" s="3" t="s">
-        <v>1633</v>
+        <v>446</v>
       </c>
       <c r="B1865" s="3" t="s">
-        <v>468</v>
+        <v>265</v>
       </c>
       <c r="C1865" s="1" t="s">
         <v>8</v>
@@ -60481,10 +60481,10 @@
         <v>9</v>
       </c>
       <c r="E1865" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="F1865" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G1865" t="s">
         <v>9</v>
@@ -60493,15 +60493,15 @@
         <v>18</v>
       </c>
       <c r="I1865" s="1" t="s">
-        <v>46</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1866" s="3" t="s">
-        <v>638</v>
+        <v>1633</v>
       </c>
       <c r="B1866" s="3" t="s">
-        <v>535</v>
+        <v>468</v>
       </c>
       <c r="C1866" s="1" t="s">
         <v>8</v>
@@ -60510,10 +60510,10 @@
         <v>9</v>
       </c>
       <c r="E1866" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="F1866" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G1866" t="s">
         <v>9</v>
@@ -60522,15 +60522,15 @@
         <v>18</v>
       </c>
       <c r="I1866" s="1" t="s">
-        <v>120</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1867" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1867" s="3" t="s">
-        <v>282</v>
+        <v>638</v>
       </c>
       <c r="B1867" s="3" t="s">
-        <v>84</v>
+        <v>535</v>
       </c>
       <c r="C1867" s="1" t="s">
         <v>8</v>
@@ -60539,27 +60539,27 @@
         <v>9</v>
       </c>
       <c r="E1867" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="F1867" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G1867" t="s">
         <v>9</v>
       </c>
       <c r="H1867" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1867" s="1" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1868" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1868" s="3" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="B1868" s="3" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="C1868" s="1" t="s">
         <v>8</v>
@@ -60568,27 +60568,27 @@
         <v>9</v>
       </c>
       <c r="E1868" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="F1868" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1868" t="s">
         <v>9</v>
       </c>
       <c r="H1868" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1868" s="1" t="s">
-        <v>323</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1869" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1869" s="3" t="s">
-        <v>1161</v>
+        <v>121</v>
       </c>
       <c r="B1869" s="3" t="s">
-        <v>396</v>
+        <v>103</v>
       </c>
       <c r="C1869" s="1" t="s">
         <v>8</v>
@@ -60597,7 +60597,7 @@
         <v>9</v>
       </c>
       <c r="E1869" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="F1869" t="s">
         <v>29</v>
@@ -60609,15 +60609,15 @@
         <v>18</v>
       </c>
       <c r="I1869" s="1" t="s">
-        <v>133</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1870" s="3" t="s">
-        <v>24</v>
+        <v>1161</v>
       </c>
       <c r="B1870" s="3" t="s">
-        <v>1465</v>
+        <v>396</v>
       </c>
       <c r="C1870" s="1" t="s">
         <v>8</v>
@@ -60629,24 +60629,24 @@
         <v>1889</v>
       </c>
       <c r="F1870" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="G1870" t="s">
         <v>9</v>
       </c>
       <c r="H1870" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1870" s="1" t="s">
-        <v>225</v>
+        <v>133</v>
       </c>
     </row>
     <row r="1871" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1871" s="3" t="s">
-        <v>195</v>
+        <v>24</v>
       </c>
       <c r="B1871" s="3" t="s">
-        <v>196</v>
+        <v>1465</v>
       </c>
       <c r="C1871" s="1" t="s">
         <v>8</v>
@@ -60655,10 +60655,10 @@
         <v>9</v>
       </c>
       <c r="E1871" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="F1871" t="s">
-        <v>1469</v>
+        <v>82</v>
       </c>
       <c r="G1871" t="s">
         <v>9</v>
@@ -60667,15 +60667,15 @@
         <v>12</v>
       </c>
       <c r="I1871" s="1" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1872" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1872" s="3" t="s">
-        <v>650</v>
+        <v>195</v>
       </c>
       <c r="B1872" s="3" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="C1872" s="1" t="s">
         <v>8</v>
@@ -60684,27 +60684,27 @@
         <v>9</v>
       </c>
       <c r="E1872" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="F1872" t="s">
-        <v>42</v>
+        <v>1469</v>
       </c>
       <c r="G1872" t="s">
         <v>9</v>
       </c>
       <c r="H1872" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1872" s="1" t="s">
-        <v>78</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1873" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1873" s="3" t="s">
-        <v>171</v>
+        <v>650</v>
       </c>
       <c r="B1873" s="3" t="s">
-        <v>182</v>
+        <v>222</v>
       </c>
       <c r="C1873" s="1" t="s">
         <v>8</v>
@@ -60716,7 +60716,7 @@
         <v>1891</v>
       </c>
       <c r="F1873" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G1873" t="s">
         <v>9</v>
@@ -60730,10 +60730,10 @@
     </row>
     <row r="1874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1874" s="3" t="s">
-        <v>386</v>
+        <v>171</v>
       </c>
       <c r="B1874" s="3" t="s">
-        <v>265</v>
+        <v>182</v>
       </c>
       <c r="C1874" s="1" t="s">
         <v>8</v>
@@ -60742,27 +60742,27 @@
         <v>9</v>
       </c>
       <c r="E1874" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="F1874" t="s">
-        <v>721</v>
+        <v>45</v>
       </c>
       <c r="G1874" t="s">
         <v>9</v>
       </c>
       <c r="H1874" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1874" s="1" t="s">
-        <v>225</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1875" s="3" t="s">
-        <v>68</v>
+        <v>386</v>
       </c>
       <c r="B1875" s="3" t="s">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="C1875" s="1" t="s">
         <v>8</v>
@@ -60771,27 +60771,27 @@
         <v>9</v>
       </c>
       <c r="E1875" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="F1875" t="s">
-        <v>17</v>
+        <v>721</v>
       </c>
       <c r="G1875" t="s">
         <v>9</v>
       </c>
       <c r="H1875" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1875" s="1" t="s">
-        <v>175</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1876" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1876" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B1876" s="3" t="s">
-        <v>58</v>
+        <v>278</v>
       </c>
       <c r="C1876" s="1" t="s">
         <v>8</v>
@@ -60803,7 +60803,7 @@
         <v>1893</v>
       </c>
       <c r="F1876" t="s">
-        <v>166</v>
+        <v>17</v>
       </c>
       <c r="G1876" t="s">
         <v>9</v>
@@ -60812,15 +60812,15 @@
         <v>18</v>
       </c>
       <c r="I1876" s="1" t="s">
-        <v>90</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1877" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B1877" s="3" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="C1877" s="1" t="s">
         <v>8</v>
@@ -60829,10 +60829,10 @@
         <v>9</v>
       </c>
       <c r="E1877" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1877" t="s">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="G1877" t="s">
         <v>9</v>
@@ -60841,15 +60841,15 @@
         <v>18</v>
       </c>
       <c r="I1877" s="1" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1878" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1878" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B1878" s="3" t="s">
-        <v>253</v>
+        <v>137</v>
       </c>
       <c r="C1878" s="1" t="s">
         <v>8</v>
@@ -60858,10 +60858,10 @@
         <v>9</v>
       </c>
       <c r="E1878" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="F1878" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="G1878" t="s">
         <v>9</v>
@@ -60870,7 +60870,7 @@
         <v>18</v>
       </c>
       <c r="I1878" s="1" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
     </row>
     <row r="1879" spans="1:9" x14ac:dyDescent="0.25">
@@ -60887,7 +60887,7 @@
         <v>9</v>
       </c>
       <c r="E1879" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="F1879" t="s">
         <v>9</v>
@@ -60904,10 +60904,10 @@
     </row>
     <row r="1880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1880" s="3" t="s">
-        <v>408</v>
+        <v>70</v>
       </c>
       <c r="B1880" s="3" t="s">
-        <v>1280</v>
+        <v>253</v>
       </c>
       <c r="C1880" s="1" t="s">
         <v>8</v>
@@ -60916,10 +60916,10 @@
         <v>9</v>
       </c>
       <c r="E1880" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="F1880" t="s">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="G1880" t="s">
         <v>9</v>
@@ -60933,10 +60933,10 @@
     </row>
     <row r="1881" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1881" s="3" t="s">
-        <v>1898</v>
+        <v>408</v>
       </c>
       <c r="B1881" s="3" t="s">
-        <v>1899</v>
+        <v>1280</v>
       </c>
       <c r="C1881" s="1" t="s">
         <v>8</v>
@@ -60945,27 +60945,27 @@
         <v>9</v>
       </c>
       <c r="E1881" t="s">
-        <v>1900</v>
+        <v>1897</v>
       </c>
       <c r="F1881" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="G1881" t="s">
         <v>9</v>
       </c>
       <c r="H1881" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1881" s="1" t="s">
-        <v>220</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1882" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1882" s="3" t="s">
-        <v>61</v>
+        <v>1898</v>
       </c>
       <c r="B1882" s="3" t="s">
-        <v>1165</v>
+        <v>1899</v>
       </c>
       <c r="C1882" s="1" t="s">
         <v>8</v>
@@ -60974,27 +60974,27 @@
         <v>9</v>
       </c>
       <c r="E1882" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="F1882" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1882" t="s">
         <v>9</v>
       </c>
       <c r="H1882" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1882" s="1" t="s">
-        <v>169</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1883" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1883" s="3" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="B1883" s="3" t="s">
-        <v>442</v>
+        <v>1165</v>
       </c>
       <c r="C1883" s="1" t="s">
         <v>8</v>
@@ -61003,7 +61003,7 @@
         <v>9</v>
       </c>
       <c r="E1883" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="F1883" t="s">
         <v>29</v>
@@ -61012,10 +61012,10 @@
         <v>9</v>
       </c>
       <c r="H1883" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1883" s="1" t="s">
-        <v>13</v>
+        <v>169</v>
       </c>
     </row>
     <row r="1884" spans="1:9" x14ac:dyDescent="0.25">
@@ -61023,7 +61023,7 @@
         <v>96</v>
       </c>
       <c r="B1884" s="3" t="s">
-        <v>99</v>
+        <v>442</v>
       </c>
       <c r="C1884" s="1" t="s">
         <v>8</v>
@@ -61035,7 +61035,7 @@
         <v>1902</v>
       </c>
       <c r="F1884" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G1884" t="s">
         <v>9</v>
@@ -61049,22 +61049,22 @@
     </row>
     <row r="1885" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1885" s="3" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B1885" s="3" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="C1885" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1885" t="s">
-        <v>184</v>
+        <v>9</v>
       </c>
       <c r="E1885" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="F1885" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="G1885" t="s">
         <v>9</v>
@@ -61073,21 +61073,21 @@
         <v>12</v>
       </c>
       <c r="I1885" s="1" t="s">
-        <v>185</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1886" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1886" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B1886" s="3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C1886" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1886" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E1886" t="s">
         <v>1903</v>
@@ -61102,27 +61102,27 @@
         <v>12</v>
       </c>
       <c r="I1886" s="1" t="s">
-        <v>64</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1887" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1887" s="3" t="s">
-        <v>277</v>
+        <v>87</v>
       </c>
       <c r="B1887" s="3" t="s">
-        <v>278</v>
+        <v>62</v>
       </c>
       <c r="C1887" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1887" t="s">
-        <v>9</v>
+        <v>186</v>
       </c>
       <c r="E1887" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="F1887" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G1887" t="s">
         <v>9</v>
@@ -61131,15 +61131,15 @@
         <v>12</v>
       </c>
       <c r="I1887" s="1" t="s">
-        <v>194</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1888" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1888" s="3" t="s">
-        <v>585</v>
+        <v>277</v>
       </c>
       <c r="B1888" s="3" t="s">
-        <v>523</v>
+        <v>278</v>
       </c>
       <c r="C1888" s="1" t="s">
         <v>8</v>
@@ -61148,27 +61148,27 @@
         <v>9</v>
       </c>
       <c r="E1888" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="F1888" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="G1888" t="s">
         <v>9</v>
       </c>
       <c r="H1888" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1888" s="1" t="s">
-        <v>78</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1889" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1889" s="3" t="s">
-        <v>318</v>
+        <v>585</v>
       </c>
       <c r="B1889" s="3" t="s">
-        <v>115</v>
+        <v>523</v>
       </c>
       <c r="C1889" s="1" t="s">
         <v>8</v>
@@ -61177,24 +61177,24 @@
         <v>9</v>
       </c>
       <c r="E1889" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="F1889" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="G1889" t="s">
         <v>9</v>
       </c>
       <c r="H1889" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1889" s="1" t="s">
-        <v>239</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1890" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1890" s="3" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="B1890" s="3" t="s">
         <v>115</v>
@@ -61209,7 +61209,7 @@
         <v>1906</v>
       </c>
       <c r="F1890" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="G1890" t="s">
         <v>9</v>
@@ -61223,10 +61223,10 @@
     </row>
     <row r="1891" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1891" s="3" t="s">
-        <v>638</v>
+        <v>206</v>
       </c>
       <c r="B1891" s="3" t="s">
-        <v>430</v>
+        <v>115</v>
       </c>
       <c r="C1891" s="1" t="s">
         <v>8</v>
@@ -61235,10 +61235,10 @@
         <v>9</v>
       </c>
       <c r="E1891" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="F1891" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="G1891" t="s">
         <v>9</v>
@@ -61247,15 +61247,15 @@
         <v>12</v>
       </c>
       <c r="I1891" s="1" t="s">
-        <v>23</v>
+        <v>239</v>
       </c>
     </row>
     <row r="1892" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1892" s="3" t="s">
-        <v>65</v>
+        <v>638</v>
       </c>
       <c r="B1892" s="3" t="s">
-        <v>88</v>
+        <v>430</v>
       </c>
       <c r="C1892" s="1" t="s">
         <v>8</v>
@@ -61264,27 +61264,27 @@
         <v>9</v>
       </c>
       <c r="E1892" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F1892" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="G1892" t="s">
         <v>9</v>
       </c>
       <c r="H1892" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1892" s="1" t="s">
-        <v>106</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1893" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1893" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B1893" s="3" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="C1893" s="1" t="s">
         <v>8</v>
@@ -61293,7 +61293,7 @@
         <v>9</v>
       </c>
       <c r="E1893" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="F1893" t="s">
         <v>17</v>
@@ -61302,18 +61302,18 @@
         <v>9</v>
       </c>
       <c r="H1893" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1893" s="1" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
     </row>
     <row r="1894" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1894" s="3" t="s">
-        <v>727</v>
+        <v>57</v>
       </c>
       <c r="B1894" s="3" t="s">
-        <v>193</v>
+        <v>58</v>
       </c>
       <c r="C1894" s="1" t="s">
         <v>8</v>
@@ -61334,24 +61334,24 @@
         <v>12</v>
       </c>
       <c r="I1894" s="1" t="s">
-        <v>187</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1895" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1895" s="3" t="s">
-        <v>135</v>
+        <v>727</v>
       </c>
       <c r="B1895" s="3" t="s">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="C1895" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1895" t="s">
-        <v>184</v>
+        <v>9</v>
       </c>
       <c r="E1895" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="F1895" t="s">
         <v>17</v>
@@ -61363,24 +61363,24 @@
         <v>12</v>
       </c>
       <c r="I1895" s="1" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
     </row>
     <row r="1896" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1896" s="3" t="s">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="B1896" s="3" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="C1896" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1896" t="s">
-        <v>9</v>
+        <v>184</v>
       </c>
       <c r="E1896" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="F1896" t="s">
         <v>17</v>
@@ -61389,18 +61389,18 @@
         <v>9</v>
       </c>
       <c r="H1896" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1896" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="1897" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1897" s="3" t="s">
-        <v>206</v>
+        <v>68</v>
       </c>
       <c r="B1897" s="3" t="s">
-        <v>207</v>
+        <v>278</v>
       </c>
       <c r="C1897" s="1" t="s">
         <v>8</v>
@@ -61409,10 +61409,10 @@
         <v>9</v>
       </c>
       <c r="E1897" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="F1897" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="G1897" t="s">
         <v>9</v>
@@ -61421,15 +61421,15 @@
         <v>18</v>
       </c>
       <c r="I1897" s="1" t="s">
-        <v>299</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1898" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1898" s="3" t="s">
-        <v>1913</v>
+        <v>206</v>
       </c>
       <c r="B1898" s="3" t="s">
-        <v>1914</v>
+        <v>207</v>
       </c>
       <c r="C1898" s="1" t="s">
         <v>8</v>
@@ -61438,27 +61438,27 @@
         <v>9</v>
       </c>
       <c r="E1898" t="s">
-        <v>1915</v>
+        <v>1912</v>
       </c>
       <c r="F1898" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="G1898" t="s">
         <v>9</v>
       </c>
       <c r="H1898" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1898" s="1" t="s">
-        <v>239</v>
+        <v>299</v>
       </c>
     </row>
     <row r="1899" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1899" s="3" t="s">
-        <v>36</v>
+        <v>1913</v>
       </c>
       <c r="B1899" s="3" t="s">
-        <v>156</v>
+        <v>1914</v>
       </c>
       <c r="C1899" s="1" t="s">
         <v>8</v>
@@ -61470,7 +61470,7 @@
         <v>1915</v>
       </c>
       <c r="F1899" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="G1899" t="s">
         <v>9</v>
@@ -61484,19 +61484,19 @@
     </row>
     <row r="1900" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1900" s="3" t="s">
-        <v>277</v>
+        <v>36</v>
       </c>
       <c r="B1900" s="3" t="s">
-        <v>1916</v>
+        <v>156</v>
       </c>
       <c r="C1900" s="1" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="D1900" t="s">
         <v>9</v>
       </c>
       <c r="E1900" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="F1900" t="s">
         <v>82</v>
@@ -61505,21 +61505,21 @@
         <v>9</v>
       </c>
       <c r="H1900" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1900" s="1" t="s">
-        <v>120</v>
+        <v>239</v>
       </c>
     </row>
     <row r="1901" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1901" s="3" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
       <c r="B1901" s="3" t="s">
-        <v>37</v>
+        <v>1916</v>
       </c>
       <c r="C1901" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D1901" t="s">
         <v>9</v>
@@ -61542,13 +61542,13 @@
     </row>
     <row r="1902" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1902" s="3" t="s">
-        <v>1918</v>
+        <v>43</v>
       </c>
       <c r="B1902" s="3" t="s">
-        <v>959</v>
+        <v>37</v>
       </c>
       <c r="C1902" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D1902" t="s">
         <v>9</v>
@@ -61566,44 +61566,44 @@
         <v>18</v>
       </c>
       <c r="I1902" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1903" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1903" s="3" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="B1903" s="3" t="s">
-        <v>669</v>
+        <v>959</v>
       </c>
       <c r="C1903" s="1" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="D1903" t="s">
         <v>9</v>
       </c>
       <c r="E1903" t="s">
-        <v>1920</v>
+        <v>1917</v>
       </c>
       <c r="F1903" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="G1903" t="s">
         <v>9</v>
       </c>
       <c r="H1903" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1903" s="1" t="s">
-        <v>220</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1904" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1904" s="3" t="s">
-        <v>727</v>
+        <v>1919</v>
       </c>
       <c r="B1904" s="3" t="s">
-        <v>740</v>
+        <v>669</v>
       </c>
       <c r="C1904" s="1" t="s">
         <v>8</v>
@@ -61612,10 +61612,10 @@
         <v>9</v>
       </c>
       <c r="E1904" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="F1904" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1904" t="s">
         <v>9</v>
@@ -61624,15 +61624,15 @@
         <v>12</v>
       </c>
       <c r="I1904" s="1" t="s">
-        <v>23</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1905" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1905" s="3" t="s">
-        <v>650</v>
+        <v>727</v>
       </c>
       <c r="B1905" s="3" t="s">
-        <v>222</v>
+        <v>740</v>
       </c>
       <c r="C1905" s="1" t="s">
         <v>8</v>
@@ -61641,27 +61641,27 @@
         <v>9</v>
       </c>
       <c r="E1905" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="F1905" t="s">
-        <v>1923</v>
+        <v>29</v>
       </c>
       <c r="G1905" t="s">
         <v>9</v>
       </c>
       <c r="H1905" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1905" s="1" t="s">
-        <v>169</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1906" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1906" s="3" t="s">
-        <v>206</v>
+        <v>650</v>
       </c>
       <c r="B1906" s="3" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="C1906" s="1" t="s">
         <v>8</v>
@@ -61670,10 +61670,10 @@
         <v>9</v>
       </c>
       <c r="E1906" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="F1906" t="s">
-        <v>42</v>
+        <v>1923</v>
       </c>
       <c r="G1906" t="s">
         <v>9</v>
@@ -61682,15 +61682,15 @@
         <v>18</v>
       </c>
       <c r="I1906" s="1" t="s">
-        <v>209</v>
+        <v>169</v>
       </c>
     </row>
     <row r="1907" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1907" s="3" t="s">
-        <v>379</v>
+        <v>206</v>
       </c>
       <c r="B1907" s="3" t="s">
-        <v>362</v>
+        <v>207</v>
       </c>
       <c r="C1907" s="1" t="s">
         <v>8</v>
@@ -61699,10 +61699,10 @@
         <v>9</v>
       </c>
       <c r="E1907" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="F1907" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="G1907" t="s">
         <v>9</v>
@@ -61711,15 +61711,15 @@
         <v>18</v>
       </c>
       <c r="I1907" s="1" t="s">
-        <v>86</v>
+        <v>209</v>
       </c>
     </row>
     <row r="1908" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1908" s="3" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="B1908" s="3" t="s">
-        <v>475</v>
+        <v>362</v>
       </c>
       <c r="C1908" s="1" t="s">
         <v>8</v>
@@ -61728,27 +61728,27 @@
         <v>9</v>
       </c>
       <c r="E1908" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="F1908" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G1908" t="s">
         <v>9</v>
       </c>
       <c r="H1908" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1908" s="1" t="s">
-        <v>160</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1909" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1909" s="3" t="s">
-        <v>57</v>
+        <v>399</v>
       </c>
       <c r="B1909" s="3" t="s">
-        <v>137</v>
+        <v>475</v>
       </c>
       <c r="C1909" s="1" t="s">
         <v>8</v>
@@ -61757,27 +61757,27 @@
         <v>9</v>
       </c>
       <c r="E1909" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="F1909" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G1909" t="s">
         <v>9</v>
       </c>
       <c r="H1909" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1909" s="1" t="s">
-        <v>46</v>
+        <v>160</v>
       </c>
     </row>
     <row r="1910" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1910" s="3" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="B1910" s="3" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="C1910" s="1" t="s">
         <v>8</v>
@@ -61786,10 +61786,10 @@
         <v>9</v>
       </c>
       <c r="E1910" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="F1910" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1910" t="s">
         <v>9</v>
@@ -61798,7 +61798,7 @@
         <v>18</v>
       </c>
       <c r="I1910" s="1" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1911" spans="1:9" x14ac:dyDescent="0.25">
@@ -61806,7 +61806,7 @@
         <v>36</v>
       </c>
       <c r="B1911" s="3" t="s">
-        <v>959</v>
+        <v>84</v>
       </c>
       <c r="C1911" s="1" t="s">
         <v>8</v>
@@ -61815,7 +61815,7 @@
         <v>9</v>
       </c>
       <c r="E1911" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="F1911" t="s">
         <v>29</v>
@@ -61827,15 +61827,15 @@
         <v>18</v>
       </c>
       <c r="I1911" s="1" t="s">
-        <v>281</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1912" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1912" s="3" t="s">
-        <v>171</v>
+        <v>36</v>
       </c>
       <c r="B1912" s="3" t="s">
-        <v>182</v>
+        <v>959</v>
       </c>
       <c r="C1912" s="1" t="s">
         <v>8</v>
@@ -61844,7 +61844,7 @@
         <v>9</v>
       </c>
       <c r="E1912" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="F1912" t="s">
         <v>29</v>
@@ -61856,15 +61856,15 @@
         <v>18</v>
       </c>
       <c r="I1912" s="1" t="s">
-        <v>110</v>
+        <v>281</v>
       </c>
     </row>
     <row r="1913" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1913" s="3" t="s">
-        <v>61</v>
+        <v>171</v>
       </c>
       <c r="B1913" s="3" t="s">
-        <v>62</v>
+        <v>182</v>
       </c>
       <c r="C1913" s="1" t="s">
         <v>8</v>
@@ -61873,7 +61873,7 @@
         <v>9</v>
       </c>
       <c r="E1913" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="F1913" t="s">
         <v>29</v>
@@ -61885,15 +61885,15 @@
         <v>18</v>
       </c>
       <c r="I1913" s="1" t="s">
-        <v>247</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1914" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1914" s="3" t="s">
-        <v>301</v>
+        <v>61</v>
       </c>
       <c r="B1914" s="3" t="s">
-        <v>212</v>
+        <v>62</v>
       </c>
       <c r="C1914" s="1" t="s">
         <v>8</v>
@@ -61902,10 +61902,10 @@
         <v>9</v>
       </c>
       <c r="E1914" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F1914" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="G1914" t="s">
         <v>9</v>
@@ -61914,15 +61914,15 @@
         <v>18</v>
       </c>
       <c r="I1914" s="1" t="s">
-        <v>74</v>
+        <v>247</v>
       </c>
     </row>
     <row r="1915" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1915" s="3" t="s">
-        <v>1132</v>
+        <v>301</v>
       </c>
       <c r="B1915" s="3" t="s">
-        <v>278</v>
+        <v>212</v>
       </c>
       <c r="C1915" s="1" t="s">
         <v>8</v>
@@ -61931,27 +61931,27 @@
         <v>9</v>
       </c>
       <c r="E1915" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="F1915" t="s">
-        <v>166</v>
+        <v>94</v>
       </c>
       <c r="G1915" t="s">
         <v>9</v>
       </c>
       <c r="H1915" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1915" s="1" t="s">
-        <v>274</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1916" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1916" s="3" t="s">
-        <v>65</v>
+        <v>1132</v>
       </c>
       <c r="B1916" s="3" t="s">
-        <v>88</v>
+        <v>278</v>
       </c>
       <c r="C1916" s="1" t="s">
         <v>8</v>
@@ -61960,27 +61960,27 @@
         <v>9</v>
       </c>
       <c r="E1916" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="F1916" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="G1916" t="s">
         <v>9</v>
       </c>
       <c r="H1916" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1916" s="1" t="s">
-        <v>90</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1917" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1917" s="3" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="B1917" s="3" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="C1917" s="1" t="s">
         <v>8</v>
@@ -61989,7 +61989,7 @@
         <v>9</v>
       </c>
       <c r="E1917" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="F1917" t="s">
         <v>42</v>
@@ -62001,15 +62001,15 @@
         <v>18</v>
       </c>
       <c r="I1917" s="1" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1918" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1918" s="3" t="s">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="B1918" s="3" t="s">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="C1918" s="1" t="s">
         <v>8</v>
@@ -62021,7 +62021,7 @@
         <v>1935</v>
       </c>
       <c r="F1918" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1918" t="s">
         <v>9</v>
@@ -62035,10 +62035,10 @@
     </row>
     <row r="1919" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1919" s="3" t="s">
-        <v>284</v>
+        <v>148</v>
       </c>
       <c r="B1919" s="3" t="s">
-        <v>283</v>
+        <v>153</v>
       </c>
       <c r="C1919" s="1" t="s">
         <v>8</v>
@@ -62047,10 +62047,10 @@
         <v>9</v>
       </c>
       <c r="E1919" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="F1919" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G1919" t="s">
         <v>9</v>
@@ -62059,15 +62059,15 @@
         <v>18</v>
       </c>
       <c r="I1919" s="1" t="s">
-        <v>281</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1920" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1920" s="3" t="s">
-        <v>135</v>
+        <v>284</v>
       </c>
       <c r="B1920" s="3" t="s">
-        <v>40</v>
+        <v>283</v>
       </c>
       <c r="C1920" s="1" t="s">
         <v>8</v>
@@ -62079,7 +62079,7 @@
         <v>1936</v>
       </c>
       <c r="F1920" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1920" t="s">
         <v>9</v>
@@ -62093,10 +62093,10 @@
     </row>
     <row r="1921" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1921" s="3" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="B1921" s="3" t="s">
-        <v>179</v>
+        <v>40</v>
       </c>
       <c r="C1921" s="1" t="s">
         <v>8</v>
@@ -62117,15 +62117,15 @@
         <v>18</v>
       </c>
       <c r="I1921" s="1" t="s">
-        <v>123</v>
+        <v>281</v>
       </c>
     </row>
     <row r="1922" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1922" s="3" t="s">
-        <v>47</v>
+        <v>121</v>
       </c>
       <c r="B1922" s="3" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="C1922" s="1" t="s">
         <v>8</v>
@@ -62134,10 +62134,10 @@
         <v>9</v>
       </c>
       <c r="E1922" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="F1922" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G1922" t="s">
         <v>9</v>
@@ -62146,15 +62146,15 @@
         <v>18</v>
       </c>
       <c r="I1922" s="1" t="s">
-        <v>167</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1923" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1923" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="B1923" s="3" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="C1923" s="1" t="s">
         <v>8</v>
@@ -62163,10 +62163,10 @@
         <v>9</v>
       </c>
       <c r="E1923" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="F1923" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1923" t="s">
         <v>9</v>
@@ -62175,15 +62175,15 @@
         <v>18</v>
       </c>
       <c r="I1923" s="1" t="s">
-        <v>392</v>
+        <v>167</v>
       </c>
     </row>
     <row r="1924" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1924" s="3" t="s">
-        <v>250</v>
+        <v>31</v>
       </c>
       <c r="B1924" s="3" t="s">
-        <v>196</v>
+        <v>84</v>
       </c>
       <c r="C1924" s="1" t="s">
         <v>8</v>
@@ -62204,15 +62204,15 @@
         <v>18</v>
       </c>
       <c r="I1924" s="1" t="s">
-        <v>234</v>
+        <v>392</v>
       </c>
     </row>
     <row r="1925" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1925" s="3" t="s">
-        <v>543</v>
+        <v>250</v>
       </c>
       <c r="B1925" s="3" t="s">
-        <v>1204</v>
+        <v>196</v>
       </c>
       <c r="C1925" s="1" t="s">
         <v>8</v>
@@ -62221,10 +62221,10 @@
         <v>9</v>
       </c>
       <c r="E1925" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="F1925" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G1925" t="s">
         <v>9</v>
@@ -62233,15 +62233,15 @@
         <v>18</v>
       </c>
       <c r="I1925" s="1" t="s">
-        <v>147</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1926" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1926" s="3" t="s">
-        <v>412</v>
+        <v>543</v>
       </c>
       <c r="B1926" s="3" t="s">
-        <v>15</v>
+        <v>1204</v>
       </c>
       <c r="C1926" s="1" t="s">
         <v>8</v>
@@ -62250,19 +62250,19 @@
         <v>9</v>
       </c>
       <c r="E1926" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="F1926" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G1926" t="s">
         <v>9</v>
       </c>
       <c r="H1926" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1926" s="1" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1927" spans="1:9" x14ac:dyDescent="0.25">
@@ -62270,7 +62270,7 @@
         <v>412</v>
       </c>
       <c r="B1927" s="3" t="s">
-        <v>357</v>
+        <v>15</v>
       </c>
       <c r="C1927" s="1" t="s">
         <v>8</v>
@@ -62282,7 +62282,7 @@
         <v>1940</v>
       </c>
       <c r="F1927" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1927" t="s">
         <v>9</v>
@@ -62296,10 +62296,10 @@
     </row>
     <row r="1928" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1928" s="3" t="s">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="B1928" s="3" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="C1928" s="1" t="s">
         <v>8</v>
@@ -62308,10 +62308,10 @@
         <v>9</v>
       </c>
       <c r="E1928" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="F1928" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G1928" t="s">
         <v>9</v>
@@ -62320,15 +62320,15 @@
         <v>12</v>
       </c>
       <c r="I1928" s="1" t="s">
-        <v>220</v>
+        <v>95</v>
       </c>
     </row>
     <row r="1929" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1929" s="3" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="B1929" s="3" t="s">
-        <v>115</v>
+        <v>311</v>
       </c>
       <c r="C1929" s="1" t="s">
         <v>8</v>
@@ -62337,27 +62337,27 @@
         <v>9</v>
       </c>
       <c r="E1929" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="F1929" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G1929" t="s">
         <v>9</v>
       </c>
       <c r="H1929" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1929" s="1" t="s">
-        <v>323</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1930" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1930" s="3" t="s">
-        <v>474</v>
+        <v>114</v>
       </c>
       <c r="B1930" s="3" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="C1930" s="1" t="s">
         <v>8</v>
@@ -62369,7 +62369,7 @@
         <v>1942</v>
       </c>
       <c r="F1930" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="G1930" t="s">
         <v>9</v>
@@ -62378,15 +62378,15 @@
         <v>18</v>
       </c>
       <c r="I1930" s="1" t="s">
-        <v>147</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1931" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1931" s="3" t="s">
-        <v>277</v>
+        <v>474</v>
       </c>
       <c r="B1931" s="3" t="s">
-        <v>278</v>
+        <v>15</v>
       </c>
       <c r="C1931" s="1" t="s">
         <v>8</v>
@@ -62395,7 +62395,7 @@
         <v>9</v>
       </c>
       <c r="E1931" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="F1931" t="s">
         <v>82</v>
@@ -62407,15 +62407,15 @@
         <v>18</v>
       </c>
       <c r="I1931" s="1" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1932" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1932" s="3" t="s">
-        <v>114</v>
+        <v>277</v>
       </c>
       <c r="B1932" s="3" t="s">
-        <v>115</v>
+        <v>278</v>
       </c>
       <c r="C1932" s="1" t="s">
         <v>8</v>
@@ -62424,24 +62424,24 @@
         <v>9</v>
       </c>
       <c r="E1932" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="F1932" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="G1932" t="s">
         <v>9</v>
       </c>
       <c r="H1932" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1932" s="1" t="s">
-        <v>143</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1933" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1933" s="3" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="B1933" s="3" t="s">
         <v>115</v>
@@ -62456,7 +62456,7 @@
         <v>1944</v>
       </c>
       <c r="F1933" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1933" t="s">
         <v>9</v>
@@ -62470,10 +62470,10 @@
     </row>
     <row r="1934" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1934" s="3" t="s">
-        <v>1347</v>
+        <v>102</v>
       </c>
       <c r="B1934" s="3" t="s">
-        <v>492</v>
+        <v>115</v>
       </c>
       <c r="C1934" s="1" t="s">
         <v>8</v>
@@ -62482,10 +62482,10 @@
         <v>9</v>
       </c>
       <c r="E1934" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="F1934" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G1934" t="s">
         <v>9</v>
@@ -62494,15 +62494,15 @@
         <v>12</v>
       </c>
       <c r="I1934" s="1" t="s">
-        <v>13</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1935" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1935" s="3" t="s">
-        <v>277</v>
+        <v>1347</v>
       </c>
       <c r="B1935" s="3" t="s">
-        <v>278</v>
+        <v>492</v>
       </c>
       <c r="C1935" s="1" t="s">
         <v>8</v>
@@ -62511,7 +62511,7 @@
         <v>9</v>
       </c>
       <c r="E1935" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="F1935" t="s">
         <v>45</v>
@@ -62520,18 +62520,18 @@
         <v>9</v>
       </c>
       <c r="H1935" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1935" s="1" t="s">
-        <v>314</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1936" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1936" s="3" t="s">
-        <v>934</v>
+        <v>277</v>
       </c>
       <c r="B1936" s="3" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="C1936" s="1" t="s">
         <v>8</v>
@@ -62540,10 +62540,10 @@
         <v>9</v>
       </c>
       <c r="E1936" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="F1936" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="G1936" t="s">
         <v>9</v>
@@ -62552,15 +62552,15 @@
         <v>18</v>
       </c>
       <c r="I1936" s="1" t="s">
-        <v>19</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1937" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1937" s="3" t="s">
-        <v>379</v>
+        <v>934</v>
       </c>
       <c r="B1937" s="3" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="C1937" s="1" t="s">
         <v>8</v>
@@ -62569,27 +62569,27 @@
         <v>9</v>
       </c>
       <c r="E1937" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="F1937" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="G1937" t="s">
         <v>9</v>
       </c>
       <c r="H1937" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1937" s="1" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1938" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1938" s="3" t="s">
-        <v>57</v>
+        <v>379</v>
       </c>
       <c r="B1938" s="3" t="s">
-        <v>137</v>
+        <v>229</v>
       </c>
       <c r="C1938" s="1" t="s">
         <v>8</v>
@@ -62598,27 +62598,27 @@
         <v>9</v>
       </c>
       <c r="E1938" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="F1938" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G1938" t="s">
         <v>9</v>
       </c>
       <c r="H1938" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1938" s="1" t="s">
-        <v>167</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1939" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1939" s="3" t="s">
-        <v>1350</v>
+        <v>57</v>
       </c>
       <c r="B1939" s="3" t="s">
-        <v>1950</v>
+        <v>137</v>
       </c>
       <c r="C1939" s="1" t="s">
         <v>8</v>
@@ -62627,27 +62627,27 @@
         <v>9</v>
       </c>
       <c r="E1939" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="F1939" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1939" t="s">
         <v>9</v>
       </c>
       <c r="H1939" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1939" s="1" t="s">
-        <v>13</v>
+        <v>167</v>
       </c>
     </row>
     <row r="1940" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1940" s="3" t="s">
-        <v>68</v>
+        <v>1350</v>
       </c>
       <c r="B1940" s="3" t="s">
-        <v>489</v>
+        <v>1950</v>
       </c>
       <c r="C1940" s="1" t="s">
         <v>8</v>
@@ -62656,7 +62656,7 @@
         <v>9</v>
       </c>
       <c r="E1940" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="F1940" t="s">
         <v>29</v>
@@ -62665,18 +62665,18 @@
         <v>9</v>
       </c>
       <c r="H1940" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1940" s="1" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1941" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1941" s="3" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="B1941" s="3" t="s">
-        <v>84</v>
+        <v>489</v>
       </c>
       <c r="C1941" s="1" t="s">
         <v>8</v>
@@ -62697,15 +62697,15 @@
         <v>18</v>
       </c>
       <c r="I1941" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1942" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1942" s="3" t="s">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="B1942" s="3" t="s">
-        <v>606</v>
+        <v>84</v>
       </c>
       <c r="C1942" s="1" t="s">
         <v>8</v>
@@ -62726,15 +62726,15 @@
         <v>18</v>
       </c>
       <c r="I1942" s="1" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1943" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1943" s="3" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="B1943" s="3" t="s">
-        <v>40</v>
+        <v>606</v>
       </c>
       <c r="C1943" s="1" t="s">
         <v>8</v>
@@ -62743,7 +62743,7 @@
         <v>9</v>
       </c>
       <c r="E1943" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="F1943" t="s">
         <v>29</v>
@@ -62752,18 +62752,18 @@
         <v>9</v>
       </c>
       <c r="H1943" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1943" s="1" t="s">
-        <v>385</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1944" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1944" s="3" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="B1944" s="3" t="s">
-        <v>317</v>
+        <v>40</v>
       </c>
       <c r="C1944" s="1" t="s">
         <v>8</v>
@@ -62772,27 +62772,27 @@
         <v>9</v>
       </c>
       <c r="E1944" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="F1944" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G1944" t="s">
         <v>9</v>
       </c>
       <c r="H1944" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1944" s="1" t="s">
-        <v>175</v>
+        <v>385</v>
       </c>
     </row>
     <row r="1945" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1945" s="3" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="B1945" s="3" t="s">
-        <v>80</v>
+        <v>317</v>
       </c>
       <c r="C1945" s="1" t="s">
         <v>8</v>
@@ -62801,10 +62801,10 @@
         <v>9</v>
       </c>
       <c r="E1945" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="F1945" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G1945" t="s">
         <v>9</v>
@@ -62813,15 +62813,15 @@
         <v>18</v>
       </c>
       <c r="I1945" s="1" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
     </row>
     <row r="1946" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1946" s="3" t="s">
-        <v>469</v>
+        <v>79</v>
       </c>
       <c r="B1946" s="3" t="s">
-        <v>271</v>
+        <v>80</v>
       </c>
       <c r="C1946" s="1" t="s">
         <v>8</v>
@@ -62830,10 +62830,10 @@
         <v>9</v>
       </c>
       <c r="E1946" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="F1946" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G1946" t="s">
         <v>9</v>
@@ -62842,15 +62842,15 @@
         <v>18</v>
       </c>
       <c r="I1946" s="1" t="s">
-        <v>90</v>
+        <v>151</v>
       </c>
     </row>
     <row r="1947" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1947" s="3" t="s">
-        <v>75</v>
+        <v>469</v>
       </c>
       <c r="B1947" s="3" t="s">
-        <v>108</v>
+        <v>271</v>
       </c>
       <c r="C1947" s="1" t="s">
         <v>8</v>
@@ -62859,10 +62859,10 @@
         <v>9</v>
       </c>
       <c r="E1947" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="F1947" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G1947" t="s">
         <v>9</v>
@@ -62871,15 +62871,15 @@
         <v>18</v>
       </c>
       <c r="I1947" s="1" t="s">
-        <v>247</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1948" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1948" s="3" t="s">
-        <v>144</v>
+        <v>75</v>
       </c>
       <c r="B1948" s="3" t="s">
-        <v>521</v>
+        <v>108</v>
       </c>
       <c r="C1948" s="1" t="s">
         <v>8</v>
@@ -62888,7 +62888,7 @@
         <v>9</v>
       </c>
       <c r="E1948" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="F1948" t="s">
         <v>29</v>
@@ -62900,15 +62900,15 @@
         <v>18</v>
       </c>
       <c r="I1948" s="1" t="s">
-        <v>203</v>
+        <v>247</v>
       </c>
     </row>
     <row r="1949" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1949" s="3" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="B1949" s="3" t="s">
-        <v>137</v>
+        <v>521</v>
       </c>
       <c r="C1949" s="1" t="s">
         <v>8</v>
@@ -62917,7 +62917,7 @@
         <v>9</v>
       </c>
       <c r="E1949" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="F1949" t="s">
         <v>29</v>
@@ -62929,15 +62929,15 @@
         <v>18</v>
       </c>
       <c r="I1949" s="1" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1950" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1950" s="3" t="s">
-        <v>1317</v>
+        <v>57</v>
       </c>
       <c r="B1950" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C1950" s="1" t="s">
         <v>8</v>
@@ -62946,7 +62946,7 @@
         <v>9</v>
       </c>
       <c r="E1950" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="F1950" t="s">
         <v>29</v>
@@ -62958,15 +62958,15 @@
         <v>18</v>
       </c>
       <c r="I1950" s="1" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
     </row>
     <row r="1951" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1951" s="3" t="s">
-        <v>613</v>
+        <v>1317</v>
       </c>
       <c r="B1951" s="3" t="s">
-        <v>283</v>
+        <v>128</v>
       </c>
       <c r="C1951" s="1" t="s">
         <v>8</v>
@@ -62975,7 +62975,7 @@
         <v>9</v>
       </c>
       <c r="E1951" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="F1951" t="s">
         <v>29</v>
@@ -62987,15 +62987,15 @@
         <v>18</v>
       </c>
       <c r="I1951" s="1" t="s">
-        <v>74</v>
+        <v>203</v>
       </c>
     </row>
     <row r="1952" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1952" s="3" t="s">
-        <v>650</v>
+        <v>613</v>
       </c>
       <c r="B1952" s="3" t="s">
-        <v>222</v>
+        <v>283</v>
       </c>
       <c r="C1952" s="1" t="s">
         <v>8</v>
@@ -63004,10 +63004,10 @@
         <v>9</v>
       </c>
       <c r="E1952" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="F1952" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G1952" t="s">
         <v>9</v>
@@ -63016,15 +63016,15 @@
         <v>18</v>
       </c>
       <c r="I1952" s="1" t="s">
-        <v>281</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1953" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1953" s="3" t="s">
-        <v>70</v>
+        <v>650</v>
       </c>
       <c r="B1953" s="3" t="s">
-        <v>27</v>
+        <v>222</v>
       </c>
       <c r="C1953" s="1" t="s">
         <v>8</v>
@@ -63033,27 +63033,27 @@
         <v>9</v>
       </c>
       <c r="E1953" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="F1953" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1953" t="s">
         <v>9</v>
       </c>
       <c r="H1953" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1953" s="1" t="s">
-        <v>326</v>
+        <v>281</v>
       </c>
     </row>
     <row r="1954" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1954" s="3" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B1954" s="3" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="C1954" s="1" t="s">
         <v>8</v>
@@ -63062,7 +63062,7 @@
         <v>9</v>
       </c>
       <c r="E1954" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="F1954" t="s">
         <v>29</v>
@@ -63071,18 +63071,18 @@
         <v>9</v>
       </c>
       <c r="H1954" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1954" s="1" t="s">
-        <v>246</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1955" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1955" s="3" t="s">
-        <v>585</v>
+        <v>57</v>
       </c>
       <c r="B1955" s="3" t="s">
-        <v>513</v>
+        <v>137</v>
       </c>
       <c r="C1955" s="1" t="s">
         <v>8</v>
@@ -63091,7 +63091,7 @@
         <v>9</v>
       </c>
       <c r="E1955" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="F1955" t="s">
         <v>29</v>
@@ -63103,15 +63103,15 @@
         <v>18</v>
       </c>
       <c r="I1955" s="1" t="s">
-        <v>323</v>
+        <v>246</v>
       </c>
     </row>
     <row r="1956" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1956" s="3" t="s">
-        <v>638</v>
+        <v>585</v>
       </c>
       <c r="B1956" s="3" t="s">
-        <v>535</v>
+        <v>513</v>
       </c>
       <c r="C1956" s="1" t="s">
         <v>8</v>
@@ -63120,10 +63120,10 @@
         <v>9</v>
       </c>
       <c r="E1956" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="F1956" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G1956" t="s">
         <v>9</v>
@@ -63132,15 +63132,15 @@
         <v>18</v>
       </c>
       <c r="I1956" s="1" t="s">
-        <v>120</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1957" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1957" s="3" t="s">
-        <v>1967</v>
+        <v>638</v>
       </c>
       <c r="B1957" s="3" t="s">
-        <v>1664</v>
+        <v>535</v>
       </c>
       <c r="C1957" s="1" t="s">
         <v>8</v>
@@ -63149,27 +63149,27 @@
         <v>9</v>
       </c>
       <c r="E1957" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="F1957" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G1957" t="s">
         <v>9</v>
       </c>
       <c r="H1957" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1957" s="1" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1958" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1958" s="3" t="s">
-        <v>79</v>
+        <v>1967</v>
       </c>
       <c r="B1958" s="3" t="s">
-        <v>80</v>
+        <v>1664</v>
       </c>
       <c r="C1958" s="1" t="s">
         <v>8</v>
@@ -63178,7 +63178,7 @@
         <v>9</v>
       </c>
       <c r="E1958" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="F1958" t="s">
         <v>45</v>
@@ -63190,15 +63190,15 @@
         <v>12</v>
       </c>
       <c r="I1958" s="1" t="s">
-        <v>220</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1959" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1959" s="3" t="s">
-        <v>474</v>
+        <v>79</v>
       </c>
       <c r="B1959" s="3" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="C1959" s="1" t="s">
         <v>8</v>
@@ -63207,27 +63207,27 @@
         <v>9</v>
       </c>
       <c r="E1959" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="F1959" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="G1959" t="s">
         <v>9</v>
       </c>
       <c r="H1959" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1959" s="1" t="s">
-        <v>19</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1960" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1960" s="3" t="s">
-        <v>412</v>
+        <v>474</v>
       </c>
       <c r="B1960" s="3" t="s">
-        <v>341</v>
+        <v>25</v>
       </c>
       <c r="C1960" s="1" t="s">
         <v>8</v>
@@ -63236,10 +63236,10 @@
         <v>9</v>
       </c>
       <c r="E1960" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="F1960" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="G1960" t="s">
         <v>9</v>
@@ -63253,10 +63253,10 @@
     </row>
     <row r="1961" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1961" s="3" t="s">
-        <v>190</v>
+        <v>412</v>
       </c>
       <c r="B1961" s="3" t="s">
-        <v>58</v>
+        <v>341</v>
       </c>
       <c r="C1961" s="1" t="s">
         <v>8</v>
@@ -63265,10 +63265,10 @@
         <v>9</v>
       </c>
       <c r="E1961" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="F1961" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G1961" t="s">
         <v>9</v>
@@ -63277,15 +63277,15 @@
         <v>18</v>
       </c>
       <c r="I1961" s="1" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1962" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1962" s="3" t="s">
-        <v>91</v>
+        <v>190</v>
       </c>
       <c r="B1962" s="3" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="C1962" s="1" t="s">
         <v>8</v>
@@ -63294,27 +63294,27 @@
         <v>9</v>
       </c>
       <c r="E1962" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="F1962" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1962" t="s">
         <v>9</v>
       </c>
       <c r="H1962" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1962" s="1" t="s">
-        <v>326</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1963" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1963" s="3" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="B1963" s="3" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="C1963" s="1" t="s">
         <v>8</v>
@@ -63323,27 +63323,27 @@
         <v>9</v>
       </c>
       <c r="E1963" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="F1963" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G1963" t="s">
         <v>9</v>
       </c>
       <c r="H1963" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1963" s="1" t="s">
-        <v>392</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1964" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1964" s="3" t="s">
-        <v>206</v>
+        <v>31</v>
       </c>
       <c r="B1964" s="3" t="s">
-        <v>207</v>
+        <v>84</v>
       </c>
       <c r="C1964" s="1" t="s">
         <v>8</v>
@@ -63352,27 +63352,27 @@
         <v>9</v>
       </c>
       <c r="E1964" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="F1964" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G1964" t="s">
         <v>9</v>
       </c>
       <c r="H1964" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1964" s="1" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
     </row>
     <row r="1965" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1965" s="3" t="s">
-        <v>650</v>
+        <v>206</v>
       </c>
       <c r="B1965" s="3" t="s">
-        <v>651</v>
+        <v>207</v>
       </c>
       <c r="C1965" s="1" t="s">
         <v>8</v>
@@ -63381,10 +63381,10 @@
         <v>9</v>
       </c>
       <c r="E1965" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="F1965" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1965" t="s">
         <v>9</v>
@@ -63393,15 +63393,15 @@
         <v>12</v>
       </c>
       <c r="I1965" s="1" t="s">
-        <v>220</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1966" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1966" s="3" t="s">
-        <v>1977</v>
+        <v>650</v>
       </c>
       <c r="B1966" s="3" t="s">
-        <v>1522</v>
+        <v>651</v>
       </c>
       <c r="C1966" s="1" t="s">
         <v>8</v>
@@ -63410,10 +63410,10 @@
         <v>9</v>
       </c>
       <c r="E1966" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="F1966" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="G1966" t="s">
         <v>9</v>
@@ -63422,15 +63422,15 @@
         <v>12</v>
       </c>
       <c r="I1966" s="1" t="s">
-        <v>51</v>
+        <v>220</v>
       </c>
     </row>
     <row r="1967" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1967" s="3" t="s">
-        <v>36</v>
+        <v>1977</v>
       </c>
       <c r="B1967" s="3" t="s">
-        <v>37</v>
+        <v>1522</v>
       </c>
       <c r="C1967" s="1" t="s">
         <v>8</v>
@@ -63439,10 +63439,10 @@
         <v>9</v>
       </c>
       <c r="E1967" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="F1967" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="G1967" t="s">
         <v>9</v>
@@ -63451,15 +63451,15 @@
         <v>12</v>
       </c>
       <c r="I1967" s="1" t="s">
-        <v>449</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1968" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1968" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B1968" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C1968" s="1" t="s">
         <v>8</v>
@@ -63471,7 +63471,7 @@
         <v>1979</v>
       </c>
       <c r="F1968" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1968" t="s">
         <v>9</v>
@@ -63488,7 +63488,7 @@
         <v>31</v>
       </c>
       <c r="B1969" s="3" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="C1969" s="1" t="s">
         <v>8</v>
@@ -63497,10 +63497,10 @@
         <v>9</v>
       </c>
       <c r="E1969" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="F1969" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G1969" t="s">
         <v>9</v>
@@ -63509,15 +63509,15 @@
         <v>12</v>
       </c>
       <c r="I1969" s="1" t="s">
-        <v>197</v>
+        <v>449</v>
       </c>
     </row>
     <row r="1970" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1970" s="3" t="s">
-        <v>374</v>
+        <v>31</v>
       </c>
       <c r="B1970" s="3" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="C1970" s="1" t="s">
         <v>8</v>
@@ -63526,27 +63526,27 @@
         <v>9</v>
       </c>
       <c r="E1970" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="F1970" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G1970" t="s">
         <v>9</v>
       </c>
       <c r="H1970" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1970" s="1" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1971" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1971" s="3" t="s">
-        <v>275</v>
+        <v>374</v>
       </c>
       <c r="B1971" s="3" t="s">
-        <v>484</v>
+        <v>103</v>
       </c>
       <c r="C1971" s="1" t="s">
         <v>8</v>
@@ -63555,10 +63555,10 @@
         <v>9</v>
       </c>
       <c r="E1971" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="F1971" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G1971" t="s">
         <v>9</v>
@@ -63567,15 +63567,15 @@
         <v>18</v>
       </c>
       <c r="I1971" s="1" t="s">
-        <v>147</v>
+        <v>234</v>
       </c>
     </row>
     <row r="1972" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1972" s="3" t="s">
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="B1972" s="3" t="s">
-        <v>207</v>
+        <v>484</v>
       </c>
       <c r="C1972" s="1" t="s">
         <v>8</v>
@@ -63584,27 +63584,27 @@
         <v>9</v>
       </c>
       <c r="E1972" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="F1972" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="G1972" t="s">
         <v>9</v>
       </c>
       <c r="H1972" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1972" s="1" t="s">
-        <v>326</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1973" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1973" s="3" t="s">
-        <v>148</v>
+        <v>206</v>
       </c>
       <c r="B1973" s="3" t="s">
-        <v>153</v>
+        <v>207</v>
       </c>
       <c r="C1973" s="1" t="s">
         <v>8</v>
@@ -63613,27 +63613,27 @@
         <v>9</v>
       </c>
       <c r="E1973" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="F1973" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="G1973" t="s">
         <v>9</v>
       </c>
       <c r="H1973" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1973" s="1" t="s">
-        <v>60</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1974" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1974" s="3" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="B1974" s="3" t="s">
-        <v>243</v>
+        <v>153</v>
       </c>
       <c r="C1974" s="1" t="s">
         <v>8</v>
@@ -63642,27 +63642,27 @@
         <v>9</v>
       </c>
       <c r="E1974" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="F1974" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="G1974" t="s">
         <v>9</v>
       </c>
       <c r="H1974" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1974" s="1" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1975" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1975" s="3" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B1975" s="3" t="s">
-        <v>58</v>
+        <v>243</v>
       </c>
       <c r="C1975" s="1" t="s">
         <v>8</v>
@@ -63671,10 +63671,10 @@
         <v>9</v>
       </c>
       <c r="E1975" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="F1975" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="G1975" t="s">
         <v>9</v>
@@ -63683,15 +63683,15 @@
         <v>12</v>
       </c>
       <c r="I1975" s="1" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
     </row>
     <row r="1976" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1976" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B1976" s="3" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="C1976" s="1" t="s">
         <v>8</v>
@@ -63700,10 +63700,10 @@
         <v>9</v>
       </c>
       <c r="E1976" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="F1976" t="s">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c r="G1976" t="s">
         <v>9</v>
@@ -63712,15 +63712,15 @@
         <v>12</v>
       </c>
       <c r="I1976" s="1" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1977" s="3" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B1977" s="3" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="C1977" s="1" t="s">
         <v>8</v>
@@ -63732,24 +63732,24 @@
         <v>1987</v>
       </c>
       <c r="F1977" t="s">
-        <v>166</v>
+        <v>29</v>
       </c>
       <c r="G1977" t="s">
         <v>9</v>
       </c>
       <c r="H1977" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1977" s="1" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1978" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1978" s="3" t="s">
-        <v>683</v>
+        <v>26</v>
       </c>
       <c r="B1978" s="3" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="C1978" s="1" t="s">
         <v>8</v>
@@ -63758,10 +63758,10 @@
         <v>9</v>
       </c>
       <c r="E1978" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="F1978" t="s">
-        <v>1989</v>
+        <v>166</v>
       </c>
       <c r="G1978" t="s">
         <v>9</v>
@@ -63770,15 +63770,15 @@
         <v>18</v>
       </c>
       <c r="I1978" s="1" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1979" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1979" s="3" t="s">
-        <v>206</v>
+        <v>683</v>
       </c>
       <c r="B1979" s="3" t="s">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="C1979" s="1" t="s">
         <v>8</v>
@@ -63787,59 +63787,59 @@
         <v>9</v>
       </c>
       <c r="E1979" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="F1979" t="s">
-        <v>9</v>
+        <v>1989</v>
       </c>
       <c r="G1979" t="s">
         <v>9</v>
       </c>
       <c r="H1979" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1979" s="1" t="s">
-        <v>326</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1980" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1980" s="3" t="s">
-        <v>61</v>
+        <v>206</v>
       </c>
       <c r="B1980" s="3" t="s">
-        <v>583</v>
+        <v>207</v>
       </c>
       <c r="C1980" s="1" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="D1980" t="s">
         <v>9</v>
       </c>
       <c r="E1980" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="F1980" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="G1980" t="s">
         <v>9</v>
       </c>
       <c r="H1980" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1980" s="1" t="s">
-        <v>60</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1981" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1981" s="3" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="B1981" s="3" t="s">
-        <v>1992</v>
+        <v>583</v>
       </c>
       <c r="C1981" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D1981" t="s">
         <v>9</v>
@@ -63862,10 +63862,10 @@
     </row>
     <row r="1982" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1982" s="3" t="s">
-        <v>1993</v>
+        <v>87</v>
       </c>
       <c r="B1982" s="3" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="C1982" s="1" t="s">
         <v>54</v>
@@ -63886,15 +63886,15 @@
         <v>18</v>
       </c>
       <c r="I1982" s="1" t="s">
-        <v>151</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1983" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1983" s="3" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B1983" s="3" t="s">
-        <v>137</v>
+        <v>1993</v>
       </c>
       <c r="C1983" s="1" t="s">
         <v>54</v>
@@ -63915,27 +63915,27 @@
         <v>18</v>
       </c>
       <c r="I1983" s="1" t="s">
-        <v>60</v>
+        <v>151</v>
       </c>
     </row>
     <row r="1984" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1984" s="3" t="s">
-        <v>284</v>
+        <v>1994</v>
       </c>
       <c r="B1984" s="3" t="s">
-        <v>283</v>
+        <v>137</v>
       </c>
       <c r="C1984" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="D1984" t="s">
         <v>9</v>
       </c>
       <c r="E1984" t="s">
-        <v>1995</v>
+        <v>1991</v>
       </c>
       <c r="F1984" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G1984" t="s">
         <v>9</v>
@@ -63944,7 +63944,7 @@
         <v>18</v>
       </c>
       <c r="I1984" s="1" t="s">
-        <v>281</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1985" spans="1:9" x14ac:dyDescent="0.25">
@@ -63964,7 +63964,7 @@
         <v>1995</v>
       </c>
       <c r="F1985" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1985" t="s">
         <v>9</v>
@@ -63978,10 +63978,10 @@
     </row>
     <row r="1986" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1986" s="3" t="s">
-        <v>61</v>
+        <v>284</v>
       </c>
       <c r="B1986" s="3" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="C1986" s="1" t="s">
         <v>8</v>
@@ -63990,10 +63990,10 @@
         <v>9</v>
       </c>
       <c r="E1986" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="F1986" t="s">
-        <v>734</v>
+        <v>29</v>
       </c>
       <c r="G1986" t="s">
         <v>9</v>
@@ -64002,15 +64002,15 @@
         <v>18</v>
       </c>
       <c r="I1986" s="1" t="s">
-        <v>167</v>
+        <v>281</v>
       </c>
     </row>
     <row r="1987" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1987" s="3" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="B1987" s="3" t="s">
-        <v>103</v>
+        <v>249</v>
       </c>
       <c r="C1987" s="1" t="s">
         <v>8</v>
@@ -64019,10 +64019,10 @@
         <v>9</v>
       </c>
       <c r="E1987" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="F1987" t="s">
-        <v>42</v>
+        <v>734</v>
       </c>
       <c r="G1987" t="s">
         <v>9</v>
@@ -64031,15 +64031,15 @@
         <v>18</v>
       </c>
       <c r="I1987" s="1" t="s">
-        <v>323</v>
+        <v>167</v>
       </c>
     </row>
     <row r="1988" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1988" s="3" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="B1988" s="3" t="s">
-        <v>406</v>
+        <v>103</v>
       </c>
       <c r="C1988" s="1" t="s">
         <v>8</v>
@@ -64048,7 +64048,7 @@
         <v>9</v>
       </c>
       <c r="E1988" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="F1988" t="s">
         <v>42</v>
@@ -64060,15 +64060,15 @@
         <v>18</v>
       </c>
       <c r="I1988" s="1" t="s">
-        <v>46</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1989" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1989" s="3" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="B1989" s="3" t="s">
-        <v>207</v>
+        <v>406</v>
       </c>
       <c r="C1989" s="1" t="s">
         <v>8</v>
@@ -64077,10 +64077,10 @@
         <v>9</v>
       </c>
       <c r="E1989" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="F1989" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="G1989" t="s">
         <v>9</v>
@@ -64089,15 +64089,15 @@
         <v>18</v>
       </c>
       <c r="I1989" s="1" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1990" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1990" s="3" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="B1990" s="3" t="s">
-        <v>108</v>
+        <v>207</v>
       </c>
       <c r="C1990" s="1" t="s">
         <v>8</v>
@@ -64106,7 +64106,7 @@
         <v>9</v>
       </c>
       <c r="E1990" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="F1990" t="s">
         <v>29</v>
@@ -64118,15 +64118,15 @@
         <v>18</v>
       </c>
       <c r="I1990" s="1" t="s">
-        <v>323</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1991" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1991" s="3" t="s">
-        <v>1167</v>
+        <v>107</v>
       </c>
       <c r="B1991" s="3" t="s">
-        <v>283</v>
+        <v>108</v>
       </c>
       <c r="C1991" s="1" t="s">
         <v>8</v>
@@ -64135,27 +64135,27 @@
         <v>9</v>
       </c>
       <c r="E1991" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="F1991" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G1991" t="s">
         <v>9</v>
       </c>
       <c r="H1991" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I1991" s="1" t="s">
-        <v>225</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1992" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1992" s="3" t="s">
-        <v>61</v>
+        <v>1167</v>
       </c>
       <c r="B1992" s="3" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="C1992" s="1" t="s">
         <v>8</v>
@@ -64164,7 +64164,7 @@
         <v>9</v>
       </c>
       <c r="E1992" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="F1992" t="s">
         <v>45</v>
@@ -64176,15 +64176,15 @@
         <v>12</v>
       </c>
       <c r="I1992" s="1" t="s">
-        <v>51</v>
+        <v>225</v>
       </c>
     </row>
     <row r="1993" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1993" s="3" t="s">
-        <v>171</v>
+        <v>61</v>
       </c>
       <c r="B1993" s="3" t="s">
-        <v>2003</v>
+        <v>249</v>
       </c>
       <c r="C1993" s="1" t="s">
         <v>8</v>
@@ -64193,7 +64193,7 @@
         <v>9</v>
       </c>
       <c r="E1993" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="F1993" t="s">
         <v>45</v>
@@ -64202,18 +64202,18 @@
         <v>9</v>
       </c>
       <c r="H1993" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I1993" s="1" t="s">
-        <v>147</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1994" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1994" s="3" t="s">
-        <v>26</v>
+        <v>171</v>
       </c>
       <c r="B1994" s="3" t="s">
-        <v>53</v>
+        <v>2003</v>
       </c>
       <c r="C1994" s="1" t="s">
         <v>8</v>
@@ -64222,10 +64222,10 @@
         <v>9</v>
       </c>
       <c r="E1994" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="F1994" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="G1994" t="s">
         <v>9</v>
@@ -64234,15 +64234,15 @@
         <v>18</v>
       </c>
       <c r="I1994" s="1" t="s">
-        <v>78</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1995" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1995" s="3" t="s">
-        <v>574</v>
+        <v>26</v>
       </c>
       <c r="B1995" s="3" t="s">
-        <v>265</v>
+        <v>53</v>
       </c>
       <c r="C1995" s="1" t="s">
         <v>8</v>
@@ -64251,7 +64251,7 @@
         <v>9</v>
       </c>
       <c r="E1995" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="F1995" t="s">
         <v>82</v>
@@ -64267,27 +64267,56 @@
       </c>
     </row>
     <row r="1996" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1996" t="s">
+      <c r="A1996" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="B1996" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1996" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1996" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1996" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F1996" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1996" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1996" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1996" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1997" t="s">
         <v>2007</v>
       </c>
-      <c r="B1996"/>
-      <c r="C1996"/>
-      <c r="D1996" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1996" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1996" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1996" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1996" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1996" t="s">
+      <c r="B1997"/>
+      <c r="C1997"/>
+      <c r="D1997" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1997" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1997" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1997" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1997" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1997" t="s">
         <v>9</v>
       </c>
     </row>
@@ -64296,7 +64325,7 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="D2:G2"/>
-    <mergeCell ref="A1996:C1996"/>
+    <mergeCell ref="A1997:C1997"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
